--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="14775" windowHeight="10050"/>
   </bookViews>
   <sheets>
     <sheet name="窗帘孔距完整对照表" sheetId="2" r:id="rId1"/>
@@ -52,7 +52,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,14 +64,22 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -218,7 +226,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -227,13 +235,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF1F8"/>
+        <fgColor rgb="FF4472C4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,21 +426,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -542,31 +535,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -575,135 +565,132 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1027,16 +1014,16 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M852"/>
-  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.25"/>
+  <dimension ref="A1:D852"/>
+  <sheetFormatPr defaultColWidth="8" defaultRowHeight="14.25" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" spans="1:13">
+    <row r="1" ht="15" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1050,7 +1037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" spans="1:13">
+    <row r="2" ht="15" customHeight="1" spans="1:4">
       <c r="A2" s="2">
         <v>150</v>
       </c>
@@ -1064,7 +1051,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:13">
+    <row r="3" ht="15" customHeight="1" spans="1:4">
       <c r="A3" s="2">
         <v>151</v>
       </c>
@@ -1078,7 +1065,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="1:13">
+    <row r="4" ht="15" customHeight="1" spans="1:4">
       <c r="A4" s="2">
         <v>152</v>
       </c>
@@ -1092,7 +1079,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:13">
+    <row r="5" ht="15" customHeight="1" spans="1:4">
       <c r="A5" s="2">
         <v>153</v>
       </c>
@@ -1106,7 +1093,7 @@
         <v>6.8</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="1:13">
+    <row r="6" ht="15" customHeight="1" spans="1:4">
       <c r="A6" s="2">
         <v>154</v>
       </c>
@@ -1120,7 +1107,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:13">
+    <row r="7" ht="15" customHeight="1" spans="1:4">
       <c r="A7" s="2">
         <v>155</v>
       </c>
@@ -1133,12 +1120,8 @@
       <c r="D7" s="3">
         <v>6.9</v>
       </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="1:13">
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:4">
       <c r="A8" s="2">
         <v>156</v>
       </c>
@@ -1152,7 +1135,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:13">
+    <row r="9" ht="15" customHeight="1" spans="1:4">
       <c r="A9" s="2">
         <v>157</v>
       </c>
@@ -1166,7 +1149,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:13">
+    <row r="10" ht="15" customHeight="1" spans="1:4">
       <c r="A10" s="2">
         <v>158</v>
       </c>
@@ -1180,7 +1163,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" spans="1:13">
+    <row r="11" ht="15" customHeight="1" spans="1:4">
       <c r="A11" s="2">
         <v>159</v>
       </c>
@@ -1194,7 +1177,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:13">
+    <row r="12" ht="15" customHeight="1" spans="1:4">
       <c r="A12" s="2">
         <v>160</v>
       </c>
@@ -1208,7 +1191,7 @@
         <v>7.1</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" spans="1:13">
+    <row r="13" ht="15" customHeight="1" spans="1:4">
       <c r="A13" s="2">
         <v>161</v>
       </c>
@@ -1222,7 +1205,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:13">
+    <row r="14" ht="15" customHeight="1" spans="1:4">
       <c r="A14" s="2">
         <v>162</v>
       </c>
@@ -1236,7 +1219,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="1:13">
+    <row r="15" ht="15" customHeight="1" spans="1:4">
       <c r="A15" s="2">
         <v>163</v>
       </c>
@@ -1250,7 +1233,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" spans="1:13">
+    <row r="16" ht="15" customHeight="1" spans="1:4">
       <c r="A16" s="2">
         <v>164</v>
       </c>
@@ -8076,24 +8059,24 @@
         <v>40</v>
       </c>
       <c r="C503" s="3">
-        <v>16.4</v>
+        <v>16.33</v>
       </c>
       <c r="D503" s="3">
-        <v>5.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="504" ht="15" customHeight="1" spans="1:4">
-      <c r="A504" s="4">
+      <c r="A504" s="2">
         <v>652</v>
       </c>
-      <c r="B504" s="4">
+      <c r="B504" s="2">
         <v>40</v>
       </c>
-      <c r="C504" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D504" s="5">
-        <v>6.2</v>
+      <c r="C504" s="3">
+        <v>16.36</v>
+      </c>
+      <c r="D504" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="505" ht="15" customHeight="1" spans="1:4">
@@ -8104,24 +8087,24 @@
         <v>40</v>
       </c>
       <c r="C505" s="3">
-        <v>16.4</v>
+        <v>16.38</v>
       </c>
       <c r="D505" s="3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="506" ht="15" customHeight="1" spans="1:4">
-      <c r="A506" s="4">
+      <c r="A506" s="2">
         <v>654</v>
       </c>
-      <c r="B506" s="4">
+      <c r="B506" s="2">
         <v>40</v>
       </c>
-      <c r="C506" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D506" s="5">
-        <v>5.3</v>
+      <c r="C506" s="3">
+        <v>16.41</v>
+      </c>
+      <c r="D506" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="507" ht="15" customHeight="1" spans="1:4">
@@ -8132,24 +8115,24 @@
         <v>40</v>
       </c>
       <c r="C507" s="3">
-        <v>16.5</v>
+        <v>16.44</v>
       </c>
       <c r="D507" s="3">
-        <v>5.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="508" ht="15" customHeight="1" spans="1:4">
-      <c r="A508" s="4">
+      <c r="A508" s="2">
         <v>656</v>
       </c>
-      <c r="B508" s="4">
+      <c r="B508" s="2">
         <v>40</v>
       </c>
-      <c r="C508" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D508" s="5">
-        <v>6.3</v>
+      <c r="C508" s="3">
+        <v>16.46</v>
+      </c>
+      <c r="D508" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="509" ht="15" customHeight="1" spans="1:4">
@@ -8160,24 +8143,24 @@
         <v>40</v>
       </c>
       <c r="C509" s="3">
-        <v>16.5</v>
+        <v>16.49</v>
       </c>
       <c r="D509" s="3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="510" ht="15" customHeight="1" spans="1:4">
-      <c r="A510" s="4">
+      <c r="A510" s="2">
         <v>658</v>
       </c>
-      <c r="B510" s="4">
+      <c r="B510" s="2">
         <v>40</v>
       </c>
-      <c r="C510" s="5">
-        <v>16.6</v>
-      </c>
-      <c r="D510" s="5">
-        <v>5.4</v>
+      <c r="C510" s="3">
+        <v>16.51</v>
+      </c>
+      <c r="D510" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="511" ht="15" customHeight="1" spans="1:4">
@@ -8188,24 +8171,24 @@
         <v>40</v>
       </c>
       <c r="C511" s="3">
-        <v>16.6</v>
+        <v>16.54</v>
       </c>
       <c r="D511" s="3">
-        <v>5.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="512" ht="15" customHeight="1" spans="1:4">
-      <c r="A512" s="4">
+      <c r="A512" s="2">
         <v>660</v>
       </c>
-      <c r="B512" s="4">
+      <c r="B512" s="2">
         <v>40</v>
       </c>
-      <c r="C512" s="5">
-        <v>16.6</v>
-      </c>
-      <c r="D512" s="5">
-        <v>6.4</v>
+      <c r="C512" s="3">
+        <v>16.56</v>
+      </c>
+      <c r="D512" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="513" ht="15" customHeight="1" spans="1:4">
@@ -8216,24 +8199,24 @@
         <v>40</v>
       </c>
       <c r="C513" s="3">
-        <v>16.6</v>
+        <v>16.59</v>
       </c>
       <c r="D513" s="3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="514" ht="15" customHeight="1" spans="1:4">
-      <c r="A514" s="4">
+      <c r="A514" s="2">
         <v>662</v>
       </c>
-      <c r="B514" s="4">
+      <c r="B514" s="2">
         <v>40</v>
       </c>
-      <c r="C514" s="5">
-        <v>16.7</v>
-      </c>
-      <c r="D514" s="5">
-        <v>5.5</v>
+      <c r="C514" s="3">
+        <v>16.62</v>
+      </c>
+      <c r="D514" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="515" ht="15" customHeight="1" spans="1:4">
@@ -8244,24 +8227,24 @@
         <v>40</v>
       </c>
       <c r="C515" s="3">
-        <v>16.7</v>
+        <v>16.64</v>
       </c>
       <c r="D515" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="516" ht="15" customHeight="1" spans="1:4">
-      <c r="A516" s="4">
+      <c r="A516" s="2">
         <v>664</v>
       </c>
-      <c r="B516" s="4">
+      <c r="B516" s="2">
         <v>40</v>
       </c>
-      <c r="C516" s="5">
-        <v>16.7</v>
-      </c>
-      <c r="D516" s="5">
-        <v>6.5</v>
+      <c r="C516" s="3">
+        <v>16.67</v>
+      </c>
+      <c r="D516" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="517" ht="15" customHeight="1" spans="1:4">
@@ -8272,24 +8255,24 @@
         <v>40</v>
       </c>
       <c r="C517" s="3">
-        <v>16.7</v>
+        <v>16.69</v>
       </c>
       <c r="D517" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="518" ht="15" customHeight="1" spans="1:4">
-      <c r="A518" s="4">
+      <c r="A518" s="2">
         <v>666</v>
       </c>
-      <c r="B518" s="4">
+      <c r="B518" s="2">
         <v>40</v>
       </c>
-      <c r="C518" s="5">
-        <v>16.8</v>
-      </c>
-      <c r="D518" s="5">
-        <v>5.6</v>
+      <c r="C518" s="3">
+        <v>16.72</v>
+      </c>
+      <c r="D518" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="519" ht="15" customHeight="1" spans="1:4">
@@ -8300,24 +8283,24 @@
         <v>40</v>
       </c>
       <c r="C519" s="3">
-        <v>16.8</v>
+        <v>16.74</v>
       </c>
       <c r="D519" s="3">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="520" ht="15" customHeight="1" spans="1:4">
-      <c r="A520" s="4">
+      <c r="A520" s="2">
         <v>668</v>
       </c>
-      <c r="B520" s="4">
+      <c r="B520" s="2">
         <v>40</v>
       </c>
-      <c r="C520" s="5">
-        <v>16.8</v>
-      </c>
-      <c r="D520" s="5">
-        <v>6.6</v>
+      <c r="C520" s="3">
+        <v>16.77</v>
+      </c>
+      <c r="D520" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="521" ht="15" customHeight="1" spans="1:4">
@@ -8328,24 +8311,24 @@
         <v>40</v>
       </c>
       <c r="C521" s="3">
-        <v>16.8</v>
+        <v>16.79</v>
       </c>
       <c r="D521" s="3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="522" ht="15" customHeight="1" spans="1:4">
-      <c r="A522" s="4">
+      <c r="A522" s="2">
         <v>670</v>
       </c>
-      <c r="B522" s="4">
+      <c r="B522" s="2">
         <v>42</v>
       </c>
-      <c r="C522" s="5">
+      <c r="C522" s="3">
         <v>16</v>
       </c>
-      <c r="D522" s="5">
-        <v>5.2</v>
+      <c r="D522" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="523" ht="15" customHeight="1" spans="1:4">
@@ -8356,24 +8339,24 @@
         <v>42</v>
       </c>
       <c r="C523" s="3">
-        <v>16</v>
+        <v>16.02</v>
       </c>
       <c r="D523" s="3">
-        <v>5.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="524" ht="15" customHeight="1" spans="1:4">
-      <c r="A524" s="4">
+      <c r="A524" s="2">
         <v>672</v>
       </c>
-      <c r="B524" s="4">
+      <c r="B524" s="2">
         <v>42</v>
       </c>
-      <c r="C524" s="5">
-        <v>16</v>
-      </c>
-      <c r="D524" s="5">
-        <v>6.2</v>
+      <c r="C524" s="3">
+        <v>16.05</v>
+      </c>
+      <c r="D524" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="525" ht="15" customHeight="1" spans="1:4">
@@ -8384,24 +8367,24 @@
         <v>42</v>
       </c>
       <c r="C525" s="3">
-        <v>16</v>
+        <v>16.07</v>
       </c>
       <c r="D525" s="3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="526" ht="15" customHeight="1" spans="1:4">
-      <c r="A526" s="4">
+      <c r="A526" s="2">
         <v>674</v>
       </c>
-      <c r="B526" s="4">
+      <c r="B526" s="2">
         <v>42</v>
       </c>
-      <c r="C526" s="5">
+      <c r="C526" s="3">
         <v>16.1</v>
       </c>
-      <c r="D526" s="5">
-        <v>5.3</v>
+      <c r="D526" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="527" ht="15" customHeight="1" spans="1:4">
@@ -8412,24 +8395,24 @@
         <v>42</v>
       </c>
       <c r="C527" s="3">
-        <v>16.1</v>
+        <v>16.12</v>
       </c>
       <c r="D527" s="3">
-        <v>5.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="528" ht="15" customHeight="1" spans="1:4">
-      <c r="A528" s="4">
+      <c r="A528" s="2">
         <v>676</v>
       </c>
-      <c r="B528" s="4">
+      <c r="B528" s="2">
         <v>42</v>
       </c>
-      <c r="C528" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="D528" s="5">
-        <v>6.7</v>
+      <c r="C528" s="3">
+        <v>16.15</v>
+      </c>
+      <c r="D528" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="529" ht="15" customHeight="1" spans="1:4">
@@ -8440,24 +8423,24 @@
         <v>42</v>
       </c>
       <c r="C529" s="3">
+        <v>16.17</v>
+      </c>
+      <c r="D529" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="530" ht="15" customHeight="1" spans="1:4">
+      <c r="A530" s="2">
+        <v>678</v>
+      </c>
+      <c r="B530" s="2">
+        <v>42</v>
+      </c>
+      <c r="C530" s="3">
         <v>16.2</v>
       </c>
-      <c r="D529" s="3">
-        <v>7.2</v>
-      </c>
-    </row>
-    <row r="530" ht="15" customHeight="1" spans="1:4">
-      <c r="A530" s="4">
-        <v>678</v>
-      </c>
-      <c r="B530" s="4">
-        <v>42</v>
-      </c>
-      <c r="C530" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D530" s="5">
-        <v>6.3</v>
+      <c r="D530" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="531" ht="15" customHeight="1" spans="1:4">
@@ -8468,24 +8451,24 @@
         <v>42</v>
       </c>
       <c r="C531" s="3">
-        <v>16.3</v>
+        <v>16.22</v>
       </c>
       <c r="D531" s="3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="532" ht="15" customHeight="1" spans="1:4">
-      <c r="A532" s="4">
+      <c r="A532" s="2">
         <v>680</v>
       </c>
-      <c r="B532" s="4">
+      <c r="B532" s="2">
         <v>42</v>
       </c>
-      <c r="C532" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D532" s="5">
-        <v>7.3</v>
+      <c r="C532" s="3">
+        <v>16.24</v>
+      </c>
+      <c r="D532" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="533" ht="15" customHeight="1" spans="1:4">
@@ -8496,24 +8479,24 @@
         <v>42</v>
       </c>
       <c r="C533" s="3">
-        <v>16.4</v>
+        <v>16.27</v>
       </c>
       <c r="D533" s="3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="534" ht="15" customHeight="1" spans="1:4">
-      <c r="A534" s="4">
+      <c r="A534" s="2">
         <v>682</v>
       </c>
-      <c r="B534" s="4">
+      <c r="B534" s="2">
         <v>42</v>
       </c>
-      <c r="C534" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D534" s="5">
-        <v>6.9</v>
+      <c r="C534" s="3">
+        <v>16.29</v>
+      </c>
+      <c r="D534" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="535" ht="15" customHeight="1" spans="1:4">
@@ -8524,24 +8507,24 @@
         <v>42</v>
       </c>
       <c r="C535" s="3">
-        <v>16.4</v>
+        <v>16.32</v>
       </c>
       <c r="D535" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="536" ht="15" customHeight="1" spans="1:4">
-      <c r="A536" s="4">
+      <c r="A536" s="2">
         <v>684</v>
       </c>
-      <c r="B536" s="4">
+      <c r="B536" s="2">
         <v>42</v>
       </c>
-      <c r="C536" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D536" s="5">
-        <v>6.5</v>
+      <c r="C536" s="3">
+        <v>16.34</v>
+      </c>
+      <c r="D536" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="537" ht="15" customHeight="1" spans="1:4">
@@ -8552,24 +8535,24 @@
         <v>42</v>
       </c>
       <c r="C537" s="3">
-        <v>16.5</v>
+        <v>16.37</v>
       </c>
       <c r="D537" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="538" ht="15" customHeight="1" spans="1:4">
-      <c r="A538" s="4">
+      <c r="A538" s="2">
         <v>686</v>
       </c>
-      <c r="B538" s="4">
+      <c r="B538" s="2">
         <v>42</v>
       </c>
-      <c r="C538" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D538" s="5">
-        <v>7.5</v>
+      <c r="C538" s="3">
+        <v>16.39</v>
+      </c>
+      <c r="D538" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="539" ht="15" customHeight="1" spans="1:4">
@@ -8580,24 +8563,24 @@
         <v>42</v>
       </c>
       <c r="C539" s="3">
-        <v>16.6</v>
+        <v>16.41</v>
       </c>
       <c r="D539" s="3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="540" ht="15" customHeight="1" spans="1:4">
-      <c r="A540" s="4">
+      <c r="A540" s="2">
         <v>688</v>
       </c>
-      <c r="B540" s="4">
+      <c r="B540" s="2">
         <v>42</v>
       </c>
-      <c r="C540" s="5">
-        <v>16.6</v>
-      </c>
-      <c r="D540" s="5">
-        <v>7.1</v>
+      <c r="C540" s="3">
+        <v>16.44</v>
+      </c>
+      <c r="D540" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="541" ht="15" customHeight="1" spans="1:4">
@@ -8608,24 +8591,24 @@
         <v>42</v>
       </c>
       <c r="C541" s="3">
-        <v>16.6</v>
+        <v>16.46</v>
       </c>
       <c r="D541" s="3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="542" ht="15" customHeight="1" spans="1:4">
-      <c r="A542" s="4">
+      <c r="A542" s="2">
         <v>690</v>
       </c>
-      <c r="B542" s="4">
+      <c r="B542" s="2">
         <v>44</v>
       </c>
-      <c r="C542" s="5">
-        <v>16</v>
-      </c>
-      <c r="D542" s="5">
-        <v>6</v>
+      <c r="C542" s="3">
+        <v>15.72</v>
+      </c>
+      <c r="D542" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="543" ht="15" customHeight="1" spans="1:4">
@@ -8636,24 +8619,24 @@
         <v>44</v>
       </c>
       <c r="C543" s="3">
-        <v>16</v>
+        <v>15.74</v>
       </c>
       <c r="D543" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="544" ht="15" customHeight="1" spans="1:4">
-      <c r="A544" s="4">
+      <c r="A544" s="2">
         <v>692</v>
       </c>
-      <c r="B544" s="4">
+      <c r="B544" s="2">
         <v>44</v>
       </c>
-      <c r="C544" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D544" s="5">
-        <v>5.6</v>
+      <c r="C544" s="3">
+        <v>15.77</v>
+      </c>
+      <c r="D544" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="545" ht="15" customHeight="1" spans="1:4">
@@ -8664,24 +8647,24 @@
         <v>44</v>
       </c>
       <c r="C545" s="3">
-        <v>16.1</v>
+        <v>15.79</v>
       </c>
       <c r="D545" s="3">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="546" ht="15" customHeight="1" spans="1:4">
-      <c r="A546" s="4">
+      <c r="A546" s="2">
         <v>694</v>
       </c>
-      <c r="B546" s="4">
+      <c r="B546" s="2">
         <v>44</v>
       </c>
-      <c r="C546" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D546" s="5">
-        <v>6.6</v>
+      <c r="C546" s="3">
+        <v>15.81</v>
+      </c>
+      <c r="D546" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="547" ht="15" customHeight="1" spans="1:4">
@@ -8692,24 +8675,24 @@
         <v>44</v>
       </c>
       <c r="C547" s="3">
-        <v>16.1</v>
+        <v>15.84</v>
       </c>
       <c r="D547" s="3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="548" ht="15" customHeight="1" spans="1:4">
-      <c r="A548" s="4">
+      <c r="A548" s="2">
         <v>696</v>
       </c>
-      <c r="B548" s="4">
+      <c r="B548" s="2">
         <v>44</v>
       </c>
-      <c r="C548" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="D548" s="5">
-        <v>5.7</v>
+      <c r="C548" s="3">
+        <v>15.86</v>
+      </c>
+      <c r="D548" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="549" ht="15" customHeight="1" spans="1:4">
@@ -8720,24 +8703,24 @@
         <v>44</v>
       </c>
       <c r="C549" s="3">
-        <v>16.2</v>
+        <v>15.88</v>
       </c>
       <c r="D549" s="3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="550" ht="15" customHeight="1" spans="1:4">
-      <c r="A550" s="4">
+      <c r="A550" s="2">
         <v>698</v>
       </c>
-      <c r="B550" s="4">
+      <c r="B550" s="2">
         <v>44</v>
       </c>
-      <c r="C550" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="D550" s="5">
-        <v>6.7</v>
+      <c r="C550" s="3">
+        <v>15.91</v>
+      </c>
+      <c r="D550" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="551" ht="15" customHeight="1" spans="1:4">
@@ -8748,24 +8731,24 @@
         <v>44</v>
       </c>
       <c r="C551" s="3">
-        <v>16.2</v>
+        <v>15.93</v>
       </c>
       <c r="D551" s="3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="552" ht="15" customHeight="1" spans="1:4">
-      <c r="A552" s="4">
+      <c r="A552" s="2">
         <v>700</v>
       </c>
-      <c r="B552" s="4">
+      <c r="B552" s="2">
         <v>44</v>
       </c>
-      <c r="C552" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D552" s="5">
-        <v>5.8</v>
+      <c r="C552" s="3">
+        <v>15.95</v>
+      </c>
+      <c r="D552" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="553" ht="15" customHeight="1" spans="1:4">
@@ -8776,24 +8759,24 @@
         <v>44</v>
       </c>
       <c r="C553" s="3">
-        <v>16.3</v>
+        <v>15.98</v>
       </c>
       <c r="D553" s="3">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="554" ht="15" customHeight="1" spans="1:4">
-      <c r="A554" s="4">
+      <c r="A554" s="2">
         <v>702</v>
       </c>
-      <c r="B554" s="4">
+      <c r="B554" s="2">
         <v>44</v>
       </c>
-      <c r="C554" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D554" s="5">
-        <v>6.8</v>
+      <c r="C554" s="3">
+        <v>16</v>
+      </c>
+      <c r="D554" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="555" ht="15" customHeight="1" spans="1:4">
@@ -8804,24 +8787,24 @@
         <v>44</v>
       </c>
       <c r="C555" s="3">
-        <v>16.3</v>
+        <v>16.02</v>
       </c>
       <c r="D555" s="3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="556" ht="15" customHeight="1" spans="1:4">
-      <c r="A556" s="4">
+      <c r="A556" s="2">
         <v>704</v>
       </c>
-      <c r="B556" s="4">
+      <c r="B556" s="2">
         <v>44</v>
       </c>
-      <c r="C556" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D556" s="5">
-        <v>5.9</v>
+      <c r="C556" s="3">
+        <v>16.05</v>
+      </c>
+      <c r="D556" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="557" ht="15" customHeight="1" spans="1:4">
@@ -8832,24 +8815,24 @@
         <v>44</v>
       </c>
       <c r="C557" s="3">
-        <v>16.4</v>
+        <v>16.07</v>
       </c>
       <c r="D557" s="3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="558" ht="15" customHeight="1" spans="1:4">
-      <c r="A558" s="4">
+      <c r="A558" s="2">
         <v>706</v>
       </c>
-      <c r="B558" s="4">
+      <c r="B558" s="2">
         <v>44</v>
       </c>
-      <c r="C558" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D558" s="5">
-        <v>6.9</v>
+      <c r="C558" s="3">
+        <v>16.09</v>
+      </c>
+      <c r="D558" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="559" ht="15" customHeight="1" spans="1:4">
@@ -8860,24 +8843,24 @@
         <v>44</v>
       </c>
       <c r="C559" s="3">
-        <v>16.4</v>
+        <v>16.12</v>
       </c>
       <c r="D559" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="560" ht="15" customHeight="1" spans="1:4">
-      <c r="A560" s="4">
+      <c r="A560" s="2">
         <v>708</v>
       </c>
-      <c r="B560" s="4">
+      <c r="B560" s="2">
         <v>44</v>
       </c>
-      <c r="C560" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D560" s="5">
-        <v>6</v>
+      <c r="C560" s="3">
+        <v>16.14</v>
+      </c>
+      <c r="D560" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="561" ht="15" customHeight="1" spans="1:4">
@@ -8888,23 +8871,23 @@
         <v>44</v>
       </c>
       <c r="C561" s="3">
-        <v>16.5</v>
+        <v>16.16</v>
       </c>
       <c r="D561" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="562" ht="15" customHeight="1" spans="1:4">
-      <c r="A562" s="4">
+      <c r="A562" s="2">
         <v>710</v>
       </c>
-      <c r="B562" s="4">
+      <c r="B562" s="2">
         <v>44</v>
       </c>
-      <c r="C562" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D562" s="5">
+      <c r="C562" s="3">
+        <v>16.19</v>
+      </c>
+      <c r="D562" s="3">
         <v>7</v>
       </c>
     </row>
@@ -8916,24 +8899,24 @@
         <v>44</v>
       </c>
       <c r="C563" s="3">
-        <v>16.5</v>
+        <v>16.21</v>
       </c>
       <c r="D563" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="564" ht="15" customHeight="1" spans="1:4">
-      <c r="A564" s="4">
+      <c r="A564" s="2">
         <v>712</v>
       </c>
-      <c r="B564" s="4">
+      <c r="B564" s="2">
         <v>44</v>
       </c>
-      <c r="C564" s="5">
-        <v>16.6</v>
-      </c>
-      <c r="D564" s="5">
-        <v>6.1</v>
+      <c r="C564" s="3">
+        <v>16.23</v>
+      </c>
+      <c r="D564" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="565" ht="15" customHeight="1" spans="1:4">
@@ -8944,24 +8927,24 @@
         <v>44</v>
       </c>
       <c r="C565" s="3">
-        <v>16.6</v>
+        <v>16.26</v>
       </c>
       <c r="D565" s="3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="566" ht="15" customHeight="1" spans="1:4">
-      <c r="A566" s="4">
+      <c r="A566" s="2">
         <v>714</v>
       </c>
-      <c r="B566" s="4">
+      <c r="B566" s="2">
         <v>44</v>
       </c>
-      <c r="C566" s="5">
-        <v>16.6</v>
-      </c>
-      <c r="D566" s="5">
-        <v>7.1</v>
+      <c r="C566" s="3">
+        <v>16.28</v>
+      </c>
+      <c r="D566" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="567" ht="15" customHeight="1" spans="1:4">
@@ -8972,24 +8955,24 @@
         <v>44</v>
       </c>
       <c r="C567" s="3">
-        <v>16.6</v>
+        <v>16.3</v>
       </c>
       <c r="D567" s="3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="568" ht="15" customHeight="1" spans="1:4">
-      <c r="A568" s="4">
+      <c r="A568" s="2">
         <v>716</v>
       </c>
-      <c r="B568" s="4">
+      <c r="B568" s="2">
         <v>46</v>
       </c>
-      <c r="C568" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D568" s="5">
-        <v>5.2</v>
+      <c r="C568" s="3">
+        <v>15.6</v>
+      </c>
+      <c r="D568" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="569" ht="15" customHeight="1" spans="1:4">
@@ -9000,24 +8983,24 @@
         <v>46</v>
       </c>
       <c r="C569" s="3">
-        <v>15.9</v>
+        <v>15.62</v>
       </c>
       <c r="D569" s="3">
-        <v>5.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="570" ht="15" customHeight="1" spans="1:4">
-      <c r="A570" s="4">
+      <c r="A570" s="2">
         <v>718</v>
       </c>
-      <c r="B570" s="4">
+      <c r="B570" s="2">
         <v>46</v>
       </c>
-      <c r="C570" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D570" s="5">
-        <v>6.2</v>
+      <c r="C570" s="3">
+        <v>15.64</v>
+      </c>
+      <c r="D570" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="571" ht="15" customHeight="1" spans="1:4">
@@ -9028,24 +9011,24 @@
         <v>46</v>
       </c>
       <c r="C571" s="3">
-        <v>15.9</v>
+        <v>15.67</v>
       </c>
       <c r="D571" s="3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="572" ht="15" customHeight="1" spans="1:4">
-      <c r="A572" s="4">
+      <c r="A572" s="2">
         <v>720</v>
       </c>
-      <c r="B572" s="4">
+      <c r="B572" s="2">
         <v>46</v>
       </c>
-      <c r="C572" s="5">
-        <v>16</v>
-      </c>
-      <c r="D572" s="5">
-        <v>5.3</v>
+      <c r="C572" s="3">
+        <v>15.69</v>
+      </c>
+      <c r="D572" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="573" ht="15" customHeight="1" spans="1:4">
@@ -9056,24 +9039,24 @@
         <v>46</v>
       </c>
       <c r="C573" s="3">
-        <v>16</v>
+        <v>15.71</v>
       </c>
       <c r="D573" s="3">
-        <v>5.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="574" ht="15" customHeight="1" spans="1:4">
-      <c r="A574" s="4">
+      <c r="A574" s="2">
         <v>722</v>
       </c>
-      <c r="B574" s="4">
+      <c r="B574" s="2">
         <v>46</v>
       </c>
-      <c r="C574" s="5">
-        <v>16</v>
-      </c>
-      <c r="D574" s="5">
-        <v>6.3</v>
+      <c r="C574" s="3">
+        <v>15.73</v>
+      </c>
+      <c r="D574" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="575" ht="15" customHeight="1" spans="1:4">
@@ -9084,24 +9067,24 @@
         <v>46</v>
       </c>
       <c r="C575" s="3">
-        <v>16</v>
+        <v>15.76</v>
       </c>
       <c r="D575" s="3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="576" ht="15" customHeight="1" spans="1:4">
-      <c r="A576" s="4">
+      <c r="A576" s="2">
         <v>724</v>
       </c>
-      <c r="B576" s="4">
+      <c r="B576" s="2">
         <v>46</v>
       </c>
-      <c r="C576" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D576" s="5">
-        <v>5.4</v>
+      <c r="C576" s="3">
+        <v>15.78</v>
+      </c>
+      <c r="D576" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="577" ht="15" customHeight="1" spans="1:4">
@@ -9112,24 +9095,24 @@
         <v>46</v>
       </c>
       <c r="C577" s="3">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="D577" s="3">
-        <v>5.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="578" ht="15" customHeight="1" spans="1:4">
-      <c r="A578" s="4">
+      <c r="A578" s="2">
         <v>726</v>
       </c>
-      <c r="B578" s="4">
+      <c r="B578" s="2">
         <v>46</v>
       </c>
-      <c r="C578" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D578" s="5">
-        <v>6.4</v>
+      <c r="C578" s="3">
+        <v>15.82</v>
+      </c>
+      <c r="D578" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="579" ht="15" customHeight="1" spans="1:4">
@@ -9140,24 +9123,24 @@
         <v>46</v>
       </c>
       <c r="C579" s="3">
-        <v>16.1</v>
+        <v>15.84</v>
       </c>
       <c r="D579" s="3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="580" ht="15" customHeight="1" spans="1:4">
-      <c r="A580" s="4">
+      <c r="A580" s="2">
         <v>728</v>
       </c>
-      <c r="B580" s="4">
+      <c r="B580" s="2">
         <v>46</v>
       </c>
-      <c r="C580" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="D580" s="5">
-        <v>5.5</v>
+      <c r="C580" s="3">
+        <v>15.87</v>
+      </c>
+      <c r="D580" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="581" ht="15" customHeight="1" spans="1:4">
@@ -9168,24 +9151,24 @@
         <v>46</v>
       </c>
       <c r="C581" s="3">
-        <v>16.2</v>
+        <v>15.89</v>
       </c>
       <c r="D581" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="582" ht="15" customHeight="1" spans="1:4">
-      <c r="A582" s="4">
+      <c r="A582" s="2">
         <v>730</v>
       </c>
-      <c r="B582" s="4">
+      <c r="B582" s="2">
         <v>46</v>
       </c>
-      <c r="C582" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="D582" s="5">
-        <v>6.5</v>
+      <c r="C582" s="3">
+        <v>15.91</v>
+      </c>
+      <c r="D582" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="583" ht="15" customHeight="1" spans="1:4">
@@ -9196,24 +9179,24 @@
         <v>46</v>
       </c>
       <c r="C583" s="3">
-        <v>16.2</v>
+        <v>15.93</v>
       </c>
       <c r="D583" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="584" ht="15" customHeight="1" spans="1:4">
-      <c r="A584" s="4">
+      <c r="A584" s="2">
         <v>732</v>
       </c>
-      <c r="B584" s="4">
+      <c r="B584" s="2">
         <v>46</v>
       </c>
-      <c r="C584" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D584" s="5">
-        <v>5.6</v>
+      <c r="C584" s="3">
+        <v>15.96</v>
+      </c>
+      <c r="D584" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="585" ht="15" customHeight="1" spans="1:4">
@@ -9224,24 +9207,24 @@
         <v>46</v>
       </c>
       <c r="C585" s="3">
-        <v>16.3</v>
+        <v>15.98</v>
       </c>
       <c r="D585" s="3">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="586" ht="15" customHeight="1" spans="1:4">
-      <c r="A586" s="4">
+      <c r="A586" s="2">
         <v>734</v>
       </c>
-      <c r="B586" s="4">
+      <c r="B586" s="2">
         <v>46</v>
       </c>
-      <c r="C586" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D586" s="5">
-        <v>6.6</v>
+      <c r="C586" s="3">
+        <v>16</v>
+      </c>
+      <c r="D586" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="587" ht="15" customHeight="1" spans="1:4">
@@ -9252,24 +9235,24 @@
         <v>46</v>
       </c>
       <c r="C587" s="3">
-        <v>16.3</v>
+        <v>16.02</v>
       </c>
       <c r="D587" s="3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="588" ht="15" customHeight="1" spans="1:4">
-      <c r="A588" s="4">
+      <c r="A588" s="2">
         <v>736</v>
       </c>
-      <c r="B588" s="4">
+      <c r="B588" s="2">
         <v>48</v>
       </c>
-      <c r="C588" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D588" s="5">
-        <v>5.6</v>
+      <c r="C588" s="3">
+        <v>15.36</v>
+      </c>
+      <c r="D588" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="589" ht="15" customHeight="1" spans="1:4">
@@ -9280,24 +9263,24 @@
         <v>48</v>
       </c>
       <c r="C589" s="3">
-        <v>15.7</v>
+        <v>15.38</v>
       </c>
       <c r="D589" s="3">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="590" ht="15" customHeight="1" spans="1:4">
-      <c r="A590" s="4">
+      <c r="A590" s="2">
         <v>738</v>
       </c>
-      <c r="B590" s="4">
+      <c r="B590" s="2">
         <v>48</v>
       </c>
-      <c r="C590" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D590" s="5">
-        <v>6.6</v>
+      <c r="C590" s="3">
+        <v>15.4</v>
+      </c>
+      <c r="D590" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="591" ht="15" customHeight="1" spans="1:4">
@@ -9308,24 +9291,24 @@
         <v>48</v>
       </c>
       <c r="C591" s="3">
-        <v>15.7</v>
+        <v>15.43</v>
       </c>
       <c r="D591" s="3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="592" ht="15" customHeight="1" spans="1:4">
-      <c r="A592" s="4">
+      <c r="A592" s="2">
         <v>740</v>
       </c>
-      <c r="B592" s="4">
+      <c r="B592" s="2">
         <v>48</v>
       </c>
-      <c r="C592" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D592" s="5">
-        <v>5.7</v>
+      <c r="C592" s="3">
+        <v>15.45</v>
+      </c>
+      <c r="D592" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="593" ht="15" customHeight="1" spans="1:4">
@@ -9336,24 +9319,24 @@
         <v>48</v>
       </c>
       <c r="C593" s="3">
-        <v>15.8</v>
+        <v>15.47</v>
       </c>
       <c r="D593" s="3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="594" ht="15" customHeight="1" spans="1:4">
-      <c r="A594" s="4">
+      <c r="A594" s="2">
         <v>742</v>
       </c>
-      <c r="B594" s="4">
+      <c r="B594" s="2">
         <v>48</v>
       </c>
-      <c r="C594" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D594" s="5">
-        <v>6.7</v>
+      <c r="C594" s="3">
+        <v>15.49</v>
+      </c>
+      <c r="D594" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="595" ht="15" customHeight="1" spans="1:4">
@@ -9364,24 +9347,24 @@
         <v>48</v>
       </c>
       <c r="C595" s="3">
-        <v>15.8</v>
+        <v>15.51</v>
       </c>
       <c r="D595" s="3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="596" ht="15" customHeight="1" spans="1:4">
-      <c r="A596" s="4">
+      <c r="A596" s="2">
         <v>744</v>
       </c>
-      <c r="B596" s="4">
+      <c r="B596" s="2">
         <v>48</v>
       </c>
-      <c r="C596" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D596" s="5">
-        <v>5.8</v>
+      <c r="C596" s="3">
+        <v>15.53</v>
+      </c>
+      <c r="D596" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="597" ht="15" customHeight="1" spans="1:4">
@@ -9392,24 +9375,24 @@
         <v>48</v>
       </c>
       <c r="C597" s="3">
-        <v>15.9</v>
+        <v>15.55</v>
       </c>
       <c r="D597" s="3">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="598" ht="15" customHeight="1" spans="1:4">
-      <c r="A598" s="4">
+      <c r="A598" s="2">
         <v>746</v>
       </c>
-      <c r="B598" s="4">
+      <c r="B598" s="2">
         <v>48</v>
       </c>
-      <c r="C598" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D598" s="5">
-        <v>6.8</v>
+      <c r="C598" s="3">
+        <v>15.57</v>
+      </c>
+      <c r="D598" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="599" ht="15" customHeight="1" spans="1:4">
@@ -9420,24 +9403,24 @@
         <v>48</v>
       </c>
       <c r="C599" s="3">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="D599" s="3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="600" ht="15" customHeight="1" spans="1:4">
-      <c r="A600" s="4">
+      <c r="A600" s="2">
         <v>748</v>
       </c>
-      <c r="B600" s="4">
+      <c r="B600" s="2">
         <v>48</v>
       </c>
-      <c r="C600" s="5">
-        <v>16</v>
-      </c>
-      <c r="D600" s="5">
-        <v>5.9</v>
+      <c r="C600" s="3">
+        <v>15.62</v>
+      </c>
+      <c r="D600" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="601" ht="15" customHeight="1" spans="1:4">
@@ -9448,24 +9431,24 @@
         <v>48</v>
       </c>
       <c r="C601" s="3">
-        <v>16</v>
+        <v>15.64</v>
       </c>
       <c r="D601" s="3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="602" ht="15" customHeight="1" spans="1:4">
-      <c r="A602" s="4">
+      <c r="A602" s="2">
         <v>750</v>
       </c>
-      <c r="B602" s="4">
+      <c r="B602" s="2">
         <v>48</v>
       </c>
-      <c r="C602" s="5">
-        <v>16</v>
-      </c>
-      <c r="D602" s="5">
-        <v>6.9</v>
+      <c r="C602" s="3">
+        <v>15.66</v>
+      </c>
+      <c r="D602" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="603" ht="15" customHeight="1" spans="1:4">
@@ -9476,24 +9459,24 @@
         <v>48</v>
       </c>
       <c r="C603" s="3">
-        <v>16</v>
+        <v>15.68</v>
       </c>
       <c r="D603" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="604" ht="15" customHeight="1" spans="1:4">
-      <c r="A604" s="4">
+      <c r="A604" s="2">
         <v>752</v>
       </c>
-      <c r="B604" s="4">
+      <c r="B604" s="2">
         <v>48</v>
       </c>
-      <c r="C604" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D604" s="5">
-        <v>6</v>
+      <c r="C604" s="3">
+        <v>15.7</v>
+      </c>
+      <c r="D604" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="605" ht="15" customHeight="1" spans="1:4">
@@ -9504,23 +9487,23 @@
         <v>48</v>
       </c>
       <c r="C605" s="3">
-        <v>16.1</v>
+        <v>15.72</v>
       </c>
       <c r="D605" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="606" ht="15" customHeight="1" spans="1:4">
-      <c r="A606" s="4">
+      <c r="A606" s="2">
         <v>754</v>
       </c>
-      <c r="B606" s="4">
+      <c r="B606" s="2">
         <v>48</v>
       </c>
-      <c r="C606" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D606" s="5">
+      <c r="C606" s="3">
+        <v>15.74</v>
+      </c>
+      <c r="D606" s="3">
         <v>7</v>
       </c>
     </row>
@@ -9532,24 +9515,24 @@
         <v>48</v>
       </c>
       <c r="C607" s="3">
-        <v>16.1</v>
+        <v>15.77</v>
       </c>
       <c r="D607" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="608" ht="15" customHeight="1" spans="1:4">
-      <c r="A608" s="4">
+      <c r="A608" s="2">
         <v>756</v>
       </c>
-      <c r="B608" s="4">
+      <c r="B608" s="2">
         <v>48</v>
       </c>
-      <c r="C608" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="D608" s="5">
-        <v>6.1</v>
+      <c r="C608" s="3">
+        <v>15.79</v>
+      </c>
+      <c r="D608" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="609" ht="15" customHeight="1" spans="1:4">
@@ -9560,24 +9543,24 @@
         <v>48</v>
       </c>
       <c r="C609" s="3">
-        <v>16.2</v>
+        <v>15.81</v>
       </c>
       <c r="D609" s="3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="610" ht="15" customHeight="1" spans="1:4">
-      <c r="A610" s="4">
+      <c r="A610" s="2">
         <v>758</v>
       </c>
-      <c r="B610" s="4">
+      <c r="B610" s="2">
         <v>48</v>
       </c>
-      <c r="C610" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="D610" s="5">
-        <v>7.1</v>
+      <c r="C610" s="3">
+        <v>15.83</v>
+      </c>
+      <c r="D610" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="611" ht="15" customHeight="1" spans="1:4">
@@ -9588,24 +9571,24 @@
         <v>48</v>
       </c>
       <c r="C611" s="3">
-        <v>16.2</v>
+        <v>15.85</v>
       </c>
       <c r="D611" s="3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="612" ht="15" customHeight="1" spans="1:4">
-      <c r="A612" s="4">
+      <c r="A612" s="2">
         <v>760</v>
       </c>
-      <c r="B612" s="4">
+      <c r="B612" s="2">
         <v>48</v>
       </c>
-      <c r="C612" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D612" s="5">
-        <v>6.2</v>
+      <c r="C612" s="3">
+        <v>15.87</v>
+      </c>
+      <c r="D612" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="613" ht="15" customHeight="1" spans="1:4">
@@ -9616,24 +9599,24 @@
         <v>48</v>
       </c>
       <c r="C613" s="3">
-        <v>16.3</v>
+        <v>15.89</v>
       </c>
       <c r="D613" s="3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="614" ht="15" customHeight="1" spans="1:4">
-      <c r="A614" s="4">
+      <c r="A614" s="2">
         <v>762</v>
       </c>
-      <c r="B614" s="4">
+      <c r="B614" s="2">
         <v>48</v>
       </c>
-      <c r="C614" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D614" s="5">
-        <v>7.2</v>
+      <c r="C614" s="3">
+        <v>15.91</v>
+      </c>
+      <c r="D614" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="615" ht="15" customHeight="1" spans="1:4">
@@ -9644,24 +9627,24 @@
         <v>48</v>
       </c>
       <c r="C615" s="3">
-        <v>16.3</v>
+        <v>15.94</v>
       </c>
       <c r="D615" s="3">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="616" ht="15" customHeight="1" spans="1:4">
-      <c r="A616" s="4">
+      <c r="A616" s="2">
         <v>764</v>
       </c>
-      <c r="B616" s="4">
+      <c r="B616" s="2">
         <v>50</v>
       </c>
-      <c r="C616" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D616" s="5">
-        <v>5.3</v>
+      <c r="C616" s="3">
+        <v>15.31</v>
+      </c>
+      <c r="D616" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="617" ht="15" customHeight="1" spans="1:4">
@@ -9672,24 +9655,24 @@
         <v>50</v>
       </c>
       <c r="C617" s="3">
-        <v>15.7</v>
+        <v>15.33</v>
       </c>
       <c r="D617" s="3">
-        <v>5.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="618" ht="15" customHeight="1" spans="1:4">
-      <c r="A618" s="4">
+      <c r="A618" s="2">
         <v>766</v>
       </c>
-      <c r="B618" s="4">
+      <c r="B618" s="2">
         <v>50</v>
       </c>
-      <c r="C618" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D618" s="5">
-        <v>6.3</v>
+      <c r="C618" s="3">
+        <v>15.35</v>
+      </c>
+      <c r="D618" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="619" ht="15" customHeight="1" spans="1:4">
@@ -9700,24 +9683,24 @@
         <v>50</v>
       </c>
       <c r="C619" s="3">
-        <v>15.7</v>
+        <v>15.37</v>
       </c>
       <c r="D619" s="3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="620" ht="15" customHeight="1" spans="1:4">
-      <c r="A620" s="4">
+      <c r="A620" s="2">
         <v>768</v>
       </c>
-      <c r="B620" s="4">
+      <c r="B620" s="2">
         <v>50</v>
       </c>
-      <c r="C620" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D620" s="5">
-        <v>5.4</v>
+      <c r="C620" s="3">
+        <v>15.39</v>
+      </c>
+      <c r="D620" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="621" ht="15" customHeight="1" spans="1:4">
@@ -9728,24 +9711,24 @@
         <v>50</v>
       </c>
       <c r="C621" s="3">
-        <v>15.8</v>
+        <v>15.41</v>
       </c>
       <c r="D621" s="3">
-        <v>5.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="622" ht="15" customHeight="1" spans="1:4">
-      <c r="A622" s="4">
+      <c r="A622" s="2">
         <v>770</v>
       </c>
-      <c r="B622" s="4">
+      <c r="B622" s="2">
         <v>50</v>
       </c>
-      <c r="C622" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D622" s="5">
-        <v>6.4</v>
+      <c r="C622" s="3">
+        <v>15.43</v>
+      </c>
+      <c r="D622" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="623" ht="15" customHeight="1" spans="1:4">
@@ -9756,24 +9739,24 @@
         <v>50</v>
       </c>
       <c r="C623" s="3">
-        <v>15.8</v>
+        <v>15.45</v>
       </c>
       <c r="D623" s="3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="624" ht="15" customHeight="1" spans="1:4">
-      <c r="A624" s="4">
+      <c r="A624" s="2">
         <v>772</v>
       </c>
-      <c r="B624" s="4">
+      <c r="B624" s="2">
         <v>50</v>
       </c>
-      <c r="C624" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D624" s="5">
-        <v>5.5</v>
+      <c r="C624" s="3">
+        <v>15.47</v>
+      </c>
+      <c r="D624" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="625" ht="15" customHeight="1" spans="1:4">
@@ -9784,24 +9767,24 @@
         <v>50</v>
       </c>
       <c r="C625" s="3">
-        <v>15.9</v>
+        <v>15.49</v>
       </c>
       <c r="D625" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="626" ht="15" customHeight="1" spans="1:4">
-      <c r="A626" s="4">
+      <c r="A626" s="2">
         <v>774</v>
       </c>
-      <c r="B626" s="4">
+      <c r="B626" s="2">
         <v>50</v>
       </c>
-      <c r="C626" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D626" s="5">
-        <v>6.5</v>
+      <c r="C626" s="3">
+        <v>15.51</v>
+      </c>
+      <c r="D626" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="627" ht="15" customHeight="1" spans="1:4">
@@ -9812,24 +9795,24 @@
         <v>50</v>
       </c>
       <c r="C627" s="3">
-        <v>15.9</v>
+        <v>15.53</v>
       </c>
       <c r="D627" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="628" ht="15" customHeight="1" spans="1:4">
-      <c r="A628" s="4">
+      <c r="A628" s="2">
         <v>776</v>
       </c>
-      <c r="B628" s="4">
+      <c r="B628" s="2">
         <v>50</v>
       </c>
-      <c r="C628" s="5">
-        <v>16</v>
-      </c>
-      <c r="D628" s="5">
-        <v>6</v>
+      <c r="C628" s="3">
+        <v>15.55</v>
+      </c>
+      <c r="D628" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="629" ht="15" customHeight="1" spans="1:4">
@@ -9840,23 +9823,23 @@
         <v>50</v>
       </c>
       <c r="C629" s="3">
-        <v>16</v>
+        <v>15.57</v>
       </c>
       <c r="D629" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="630" ht="15" customHeight="1" spans="1:4">
-      <c r="A630" s="4">
+      <c r="A630" s="2">
         <v>778</v>
       </c>
-      <c r="B630" s="4">
+      <c r="B630" s="2">
         <v>50</v>
       </c>
-      <c r="C630" s="5">
-        <v>16</v>
-      </c>
-      <c r="D630" s="5">
+      <c r="C630" s="3">
+        <v>15.59</v>
+      </c>
+      <c r="D630" s="3">
         <v>7</v>
       </c>
     </row>
@@ -9868,24 +9851,24 @@
         <v>50</v>
       </c>
       <c r="C631" s="3">
-        <v>16</v>
+        <v>15.61</v>
       </c>
       <c r="D631" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="632" ht="15" customHeight="1" spans="1:4">
-      <c r="A632" s="4">
+      <c r="A632" s="2">
         <v>780</v>
       </c>
-      <c r="B632" s="4">
+      <c r="B632" s="2">
         <v>50</v>
       </c>
-      <c r="C632" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D632" s="5">
-        <v>6.1</v>
+      <c r="C632" s="3">
+        <v>15.63</v>
+      </c>
+      <c r="D632" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="633" ht="15" customHeight="1" spans="1:4">
@@ -9896,24 +9879,24 @@
         <v>50</v>
       </c>
       <c r="C633" s="3">
-        <v>16.1</v>
+        <v>15.65</v>
       </c>
       <c r="D633" s="3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="634" ht="15" customHeight="1" spans="1:4">
-      <c r="A634" s="4">
+      <c r="A634" s="2">
         <v>782</v>
       </c>
-      <c r="B634" s="4">
+      <c r="B634" s="2">
         <v>50</v>
       </c>
-      <c r="C634" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D634" s="5">
-        <v>7.1</v>
+      <c r="C634" s="3">
+        <v>15.67</v>
+      </c>
+      <c r="D634" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="635" ht="15" customHeight="1" spans="1:4">
@@ -9924,24 +9907,24 @@
         <v>50</v>
       </c>
       <c r="C635" s="3">
-        <v>16.1</v>
+        <v>15.69</v>
       </c>
       <c r="D635" s="3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="636" ht="15" customHeight="1" spans="1:4">
-      <c r="A636" s="4">
+      <c r="A636" s="2">
         <v>784</v>
       </c>
-      <c r="B636" s="4">
+      <c r="B636" s="2">
         <v>52</v>
       </c>
-      <c r="C636" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D636" s="5">
-        <v>5.6</v>
+      <c r="C636" s="3">
+        <v>15.1</v>
+      </c>
+      <c r="D636" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="637" ht="15" customHeight="1" spans="1:4">
@@ -9952,24 +9935,24 @@
         <v>52</v>
       </c>
       <c r="C637" s="3">
-        <v>15.4</v>
+        <v>15.12</v>
       </c>
       <c r="D637" s="3">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="638" ht="15" customHeight="1" spans="1:4">
-      <c r="A638" s="4">
+      <c r="A638" s="2">
         <v>786</v>
       </c>
-      <c r="B638" s="4">
+      <c r="B638" s="2">
         <v>52</v>
       </c>
-      <c r="C638" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D638" s="5">
-        <v>6.6</v>
+      <c r="C638" s="3">
+        <v>15.14</v>
+      </c>
+      <c r="D638" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="639" ht="15" customHeight="1" spans="1:4">
@@ -9980,24 +9963,24 @@
         <v>52</v>
       </c>
       <c r="C639" s="3">
-        <v>15.4</v>
+        <v>15.16</v>
       </c>
       <c r="D639" s="3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="640" ht="15" customHeight="1" spans="1:4">
-      <c r="A640" s="4">
+      <c r="A640" s="2">
         <v>788</v>
       </c>
-      <c r="B640" s="4">
+      <c r="B640" s="2">
         <v>52</v>
       </c>
-      <c r="C640" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D640" s="5">
-        <v>5.7</v>
+      <c r="C640" s="3">
+        <v>15.18</v>
+      </c>
+      <c r="D640" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="641" ht="15" customHeight="1" spans="1:4">
@@ -10008,24 +9991,24 @@
         <v>52</v>
       </c>
       <c r="C641" s="3">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="D641" s="3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="642" ht="15" customHeight="1" spans="1:4">
-      <c r="A642" s="4">
+      <c r="A642" s="2">
         <v>790</v>
       </c>
-      <c r="B642" s="4">
+      <c r="B642" s="2">
         <v>52</v>
       </c>
-      <c r="C642" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D642" s="5">
-        <v>6.7</v>
+      <c r="C642" s="3">
+        <v>15.22</v>
+      </c>
+      <c r="D642" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="643" ht="15" customHeight="1" spans="1:4">
@@ -10036,24 +10019,24 @@
         <v>52</v>
       </c>
       <c r="C643" s="3">
-        <v>15.5</v>
+        <v>15.24</v>
       </c>
       <c r="D643" s="3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="644" ht="15" customHeight="1" spans="1:4">
-      <c r="A644" s="4">
+      <c r="A644" s="2">
         <v>792</v>
       </c>
-      <c r="B644" s="4">
+      <c r="B644" s="2">
         <v>52</v>
       </c>
-      <c r="C644" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D644" s="5">
-        <v>5.8</v>
+      <c r="C644" s="3">
+        <v>15.25</v>
+      </c>
+      <c r="D644" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="645" ht="15" customHeight="1" spans="1:4">
@@ -10064,24 +10047,24 @@
         <v>52</v>
       </c>
       <c r="C645" s="3">
-        <v>15.6</v>
+        <v>15.27</v>
       </c>
       <c r="D645" s="3">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="646" ht="15" customHeight="1" spans="1:4">
-      <c r="A646" s="4">
+      <c r="A646" s="2">
         <v>794</v>
       </c>
-      <c r="B646" s="4">
+      <c r="B646" s="2">
         <v>52</v>
       </c>
-      <c r="C646" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D646" s="5">
-        <v>6.8</v>
+      <c r="C646" s="3">
+        <v>15.29</v>
+      </c>
+      <c r="D646" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="647" ht="15" customHeight="1" spans="1:4">
@@ -10092,24 +10075,24 @@
         <v>52</v>
       </c>
       <c r="C647" s="3">
-        <v>15.6</v>
+        <v>15.31</v>
       </c>
       <c r="D647" s="3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="648" ht="15" customHeight="1" spans="1:4">
-      <c r="A648" s="4">
+      <c r="A648" s="2">
         <v>796</v>
       </c>
-      <c r="B648" s="4">
+      <c r="B648" s="2">
         <v>52</v>
       </c>
-      <c r="C648" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D648" s="5">
-        <v>5.9</v>
+      <c r="C648" s="3">
+        <v>15.33</v>
+      </c>
+      <c r="D648" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="649" ht="15" customHeight="1" spans="1:4">
@@ -10120,24 +10103,24 @@
         <v>52</v>
       </c>
       <c r="C649" s="3">
-        <v>15.7</v>
+        <v>15.35</v>
       </c>
       <c r="D649" s="3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="650" ht="15" customHeight="1" spans="1:4">
-      <c r="A650" s="4">
+      <c r="A650" s="2">
         <v>798</v>
       </c>
-      <c r="B650" s="4">
+      <c r="B650" s="2">
         <v>52</v>
       </c>
-      <c r="C650" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D650" s="5">
-        <v>6.9</v>
+      <c r="C650" s="3">
+        <v>15.37</v>
+      </c>
+      <c r="D650" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="651" ht="15" customHeight="1" spans="1:4">
@@ -10148,24 +10131,24 @@
         <v>52</v>
       </c>
       <c r="C651" s="3">
-        <v>15.7</v>
+        <v>15.39</v>
       </c>
       <c r="D651" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="652" ht="15" customHeight="1" spans="1:4">
-      <c r="A652" s="4">
+      <c r="A652" s="2">
         <v>800</v>
       </c>
-      <c r="B652" s="4">
+      <c r="B652" s="2">
         <v>52</v>
       </c>
-      <c r="C652" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D652" s="5">
-        <v>6</v>
+      <c r="C652" s="3">
+        <v>15.41</v>
+      </c>
+      <c r="D652" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="653" ht="15" customHeight="1" spans="1:4">
@@ -10176,23 +10159,23 @@
         <v>52</v>
       </c>
       <c r="C653" s="3">
-        <v>15.8</v>
+        <v>15.43</v>
       </c>
       <c r="D653" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="654" ht="15" customHeight="1" spans="1:4">
-      <c r="A654" s="4">
+      <c r="A654" s="2">
         <v>802</v>
       </c>
-      <c r="B654" s="4">
+      <c r="B654" s="2">
         <v>52</v>
       </c>
-      <c r="C654" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D654" s="5">
+      <c r="C654" s="3">
+        <v>15.45</v>
+      </c>
+      <c r="D654" s="3">
         <v>7</v>
       </c>
     </row>
@@ -10204,24 +10187,24 @@
         <v>52</v>
       </c>
       <c r="C655" s="3">
-        <v>15.8</v>
+        <v>15.47</v>
       </c>
       <c r="D655" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="656" ht="15" customHeight="1" spans="1:4">
-      <c r="A656" s="4">
+      <c r="A656" s="2">
         <v>804</v>
       </c>
-      <c r="B656" s="4">
+      <c r="B656" s="2">
         <v>54</v>
       </c>
-      <c r="C656" s="5">
-        <v>15.3</v>
-      </c>
-      <c r="D656" s="5">
-        <v>5.6</v>
+      <c r="C656" s="3">
+        <v>14.91</v>
+      </c>
+      <c r="D656" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="657" ht="15" customHeight="1" spans="1:4">
@@ -10232,24 +10215,24 @@
         <v>54</v>
       </c>
       <c r="C657" s="3">
-        <v>15.3</v>
+        <v>14.92</v>
       </c>
       <c r="D657" s="3">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="658" ht="15" customHeight="1" spans="1:4">
-      <c r="A658" s="4">
+      <c r="A658" s="2">
         <v>806</v>
       </c>
-      <c r="B658" s="4">
+      <c r="B658" s="2">
         <v>54</v>
       </c>
-      <c r="C658" s="5">
-        <v>15.3</v>
-      </c>
-      <c r="D658" s="5">
-        <v>6.6</v>
+      <c r="C658" s="3">
+        <v>15</v>
+      </c>
+      <c r="D658" s="3">
+        <v>5.5</v>
       </c>
     </row>
     <row r="659" ht="15" customHeight="1" spans="1:4">
@@ -10260,24 +10243,24 @@
         <v>54</v>
       </c>
       <c r="C659" s="3">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="D659" s="3">
-        <v>7.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="660" ht="15" customHeight="1" spans="1:4">
-      <c r="A660" s="4">
+      <c r="A660" s="2">
         <v>808</v>
       </c>
-      <c r="B660" s="4">
+      <c r="B660" s="2">
         <v>54</v>
       </c>
-      <c r="C660" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D660" s="5">
-        <v>5.7</v>
+      <c r="C660" s="3">
+        <v>15</v>
+      </c>
+      <c r="D660" s="3">
+        <v>6.5</v>
       </c>
     </row>
     <row r="661" ht="15" customHeight="1" spans="1:4">
@@ -10288,24 +10271,24 @@
         <v>54</v>
       </c>
       <c r="C661" s="3">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="D661" s="3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="662" ht="15" customHeight="1" spans="1:4">
-      <c r="A662" s="4">
+      <c r="A662" s="2">
         <v>810</v>
       </c>
-      <c r="B662" s="4">
+      <c r="B662" s="2">
         <v>54</v>
       </c>
-      <c r="C662" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D662" s="5">
-        <v>6.7</v>
+      <c r="C662" s="3">
+        <v>15.02</v>
+      </c>
+      <c r="D662" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="663" ht="15" customHeight="1" spans="1:4">
@@ -10316,24 +10299,24 @@
         <v>54</v>
       </c>
       <c r="C663" s="3">
-        <v>15.4</v>
+        <v>15.04</v>
       </c>
       <c r="D663" s="3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="664" ht="15" customHeight="1" spans="1:4">
-      <c r="A664" s="4">
+      <c r="A664" s="2">
         <v>812</v>
       </c>
-      <c r="B664" s="4">
+      <c r="B664" s="2">
         <v>54</v>
       </c>
-      <c r="C664" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D664" s="5">
-        <v>5.8</v>
+      <c r="C664" s="3">
+        <v>15.06</v>
+      </c>
+      <c r="D664" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="665" ht="15" customHeight="1" spans="1:4">
@@ -10344,24 +10327,24 @@
         <v>54</v>
       </c>
       <c r="C665" s="3">
-        <v>15.5</v>
+        <v>15.08</v>
       </c>
       <c r="D665" s="3">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="666" ht="15" customHeight="1" spans="1:4">
-      <c r="A666" s="4">
+      <c r="A666" s="2">
         <v>814</v>
       </c>
-      <c r="B666" s="4">
+      <c r="B666" s="2">
         <v>54</v>
       </c>
-      <c r="C666" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D666" s="5">
-        <v>6.8</v>
+      <c r="C666" s="3">
+        <v>15.09</v>
+      </c>
+      <c r="D666" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="667" ht="15" customHeight="1" spans="1:4">
@@ -10372,24 +10355,24 @@
         <v>54</v>
       </c>
       <c r="C667" s="3">
-        <v>15.5</v>
+        <v>15.11</v>
       </c>
       <c r="D667" s="3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="668" ht="15" customHeight="1" spans="1:4">
-      <c r="A668" s="4">
+      <c r="A668" s="2">
         <v>816</v>
       </c>
-      <c r="B668" s="4">
+      <c r="B668" s="2">
         <v>54</v>
       </c>
-      <c r="C668" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D668" s="5">
-        <v>5.9</v>
+      <c r="C668" s="3">
+        <v>15.13</v>
+      </c>
+      <c r="D668" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="669" ht="15" customHeight="1" spans="1:4">
@@ -10400,24 +10383,24 @@
         <v>54</v>
       </c>
       <c r="C669" s="3">
-        <v>15.6</v>
+        <v>15.15</v>
       </c>
       <c r="D669" s="3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="670" ht="15" customHeight="1" spans="1:4">
-      <c r="A670" s="4">
+      <c r="A670" s="2">
         <v>818</v>
       </c>
-      <c r="B670" s="4">
+      <c r="B670" s="2">
         <v>54</v>
       </c>
-      <c r="C670" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D670" s="5">
-        <v>6.9</v>
+      <c r="C670" s="3">
+        <v>15.17</v>
+      </c>
+      <c r="D670" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="671" ht="15" customHeight="1" spans="1:4">
@@ -10428,24 +10411,24 @@
         <v>54</v>
       </c>
       <c r="C671" s="3">
-        <v>15.6</v>
+        <v>15.19</v>
       </c>
       <c r="D671" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="672" ht="15" customHeight="1" spans="1:4">
-      <c r="A672" s="4">
+      <c r="A672" s="2">
         <v>820</v>
       </c>
-      <c r="B672" s="4">
+      <c r="B672" s="2">
         <v>54</v>
       </c>
-      <c r="C672" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D672" s="5">
-        <v>6</v>
+      <c r="C672" s="3">
+        <v>15.21</v>
+      </c>
+      <c r="D672" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="673" ht="15" customHeight="1" spans="1:4">
@@ -10456,23 +10439,23 @@
         <v>54</v>
       </c>
       <c r="C673" s="3">
-        <v>15.7</v>
+        <v>15.23</v>
       </c>
       <c r="D673" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="674" ht="15" customHeight="1" spans="1:4">
-      <c r="A674" s="4">
+      <c r="A674" s="2">
         <v>822</v>
       </c>
-      <c r="B674" s="4">
+      <c r="B674" s="2">
         <v>54</v>
       </c>
-      <c r="C674" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D674" s="5">
+      <c r="C674" s="3">
+        <v>15.25</v>
+      </c>
+      <c r="D674" s="3">
         <v>7</v>
       </c>
     </row>
@@ -10484,24 +10467,24 @@
         <v>54</v>
       </c>
       <c r="C675" s="3">
-        <v>15.7</v>
+        <v>15.26</v>
       </c>
       <c r="D675" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="676" ht="15" customHeight="1" spans="1:4">
-      <c r="A676" s="4">
+      <c r="A676" s="2">
         <v>824</v>
       </c>
-      <c r="B676" s="4">
+      <c r="B676" s="2">
         <v>54</v>
       </c>
-      <c r="C676" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D676" s="5">
-        <v>8</v>
+      <c r="C676" s="3">
+        <v>15.28</v>
+      </c>
+      <c r="D676" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="677" ht="15" customHeight="1" spans="1:4">
@@ -10512,24 +10495,24 @@
         <v>54</v>
       </c>
       <c r="C677" s="3">
-        <v>15.7</v>
+        <v>15.3</v>
       </c>
       <c r="D677" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="678" ht="15" customHeight="1" spans="1:4">
-      <c r="A678" s="4">
+      <c r="A678" s="2">
         <v>826</v>
       </c>
-      <c r="B678" s="4">
+      <c r="B678" s="2">
         <v>54</v>
       </c>
-      <c r="C678" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D678" s="5">
-        <v>6.6</v>
+      <c r="C678" s="3">
+        <v>15.32</v>
+      </c>
+      <c r="D678" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="679" ht="15" customHeight="1" spans="1:4">
@@ -10540,24 +10523,24 @@
         <v>54</v>
       </c>
       <c r="C679" s="3">
-        <v>15.7</v>
+        <v>15.34</v>
       </c>
       <c r="D679" s="3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="680" ht="15" customHeight="1" spans="1:4">
-      <c r="A680" s="4">
+      <c r="A680" s="2">
         <v>828</v>
       </c>
-      <c r="B680" s="4">
+      <c r="B680" s="2">
         <v>54</v>
       </c>
-      <c r="C680" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D680" s="5">
-        <v>7.6</v>
+      <c r="C680" s="3">
+        <v>15.36</v>
+      </c>
+      <c r="D680" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="681" ht="15" customHeight="1" spans="1:4">
@@ -10568,24 +10551,24 @@
         <v>54</v>
       </c>
       <c r="C681" s="3">
-        <v>15.8</v>
+        <v>15.38</v>
       </c>
       <c r="D681" s="3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="682" ht="15" customHeight="1" spans="1:4">
-      <c r="A682" s="4">
+      <c r="A682" s="2">
         <v>830</v>
       </c>
-      <c r="B682" s="4">
+      <c r="B682" s="2">
         <v>54</v>
       </c>
-      <c r="C682" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D682" s="5">
-        <v>6.7</v>
+      <c r="C682" s="3">
+        <v>15.4</v>
+      </c>
+      <c r="D682" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="683" ht="15" customHeight="1" spans="1:4">
@@ -10596,24 +10579,24 @@
         <v>54</v>
       </c>
       <c r="C683" s="3">
-        <v>15.8</v>
+        <v>15.42</v>
       </c>
       <c r="D683" s="3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="684" ht="15" customHeight="1" spans="1:4">
-      <c r="A684" s="4">
+      <c r="A684" s="2">
         <v>832</v>
       </c>
-      <c r="B684" s="4">
+      <c r="B684" s="2">
         <v>54</v>
       </c>
-      <c r="C684" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D684" s="5">
-        <v>7.7</v>
+      <c r="C684" s="3">
+        <v>15.43</v>
+      </c>
+      <c r="D684" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="685" ht="15" customHeight="1" spans="1:4">
@@ -10624,24 +10607,24 @@
         <v>54</v>
       </c>
       <c r="C685" s="3">
-        <v>15.9</v>
+        <v>15.45</v>
       </c>
       <c r="D685" s="3">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="686" ht="15" customHeight="1" spans="1:4">
-      <c r="A686" s="4">
+      <c r="A686" s="2">
         <v>834</v>
       </c>
-      <c r="B686" s="4">
+      <c r="B686" s="2">
         <v>54</v>
       </c>
-      <c r="C686" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D686" s="5">
-        <v>6.8</v>
+      <c r="C686" s="3">
+        <v>15.47</v>
+      </c>
+      <c r="D686" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="687" ht="15" customHeight="1" spans="1:4">
@@ -10652,24 +10635,24 @@
         <v>54</v>
       </c>
       <c r="C687" s="3">
-        <v>15.9</v>
+        <v>15.49</v>
       </c>
       <c r="D687" s="3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="688" ht="15" customHeight="1" spans="1:4">
-      <c r="A688" s="4">
+      <c r="A688" s="2">
         <v>836</v>
       </c>
-      <c r="B688" s="4">
+      <c r="B688" s="2">
         <v>56</v>
       </c>
-      <c r="C688" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D688" s="5">
-        <v>5.8</v>
+      <c r="C688" s="3">
+        <v>15</v>
+      </c>
+      <c r="D688" s="3">
+        <v>5.5</v>
       </c>
     </row>
     <row r="689" ht="15" customHeight="1" spans="1:4">
@@ -10680,24 +10663,24 @@
         <v>56</v>
       </c>
       <c r="C689" s="3">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="D689" s="3">
-        <v>6.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="690" ht="15" customHeight="1" spans="1:4">
-      <c r="A690" s="4">
+      <c r="A690" s="2">
         <v>838</v>
       </c>
-      <c r="B690" s="4">
+      <c r="B690" s="2">
         <v>56</v>
       </c>
-      <c r="C690" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D690" s="5">
-        <v>6.8</v>
+      <c r="C690" s="3">
+        <v>15</v>
+      </c>
+      <c r="D690" s="3">
+        <v>6.5</v>
       </c>
     </row>
     <row r="691" ht="15" customHeight="1" spans="1:4">
@@ -10708,24 +10691,24 @@
         <v>56</v>
       </c>
       <c r="C691" s="3">
-        <v>15.4</v>
+        <v>15</v>
       </c>
       <c r="D691" s="3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="692" ht="15" customHeight="1" spans="1:4">
-      <c r="A692" s="4">
+      <c r="A692" s="2">
         <v>840</v>
       </c>
-      <c r="B692" s="4">
+      <c r="B692" s="2">
         <v>56</v>
       </c>
-      <c r="C692" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D692" s="5">
-        <v>5.9</v>
+      <c r="C692" s="3">
+        <v>15.02</v>
+      </c>
+      <c r="D692" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="693" ht="15" customHeight="1" spans="1:4">
@@ -10736,24 +10719,24 @@
         <v>56</v>
       </c>
       <c r="C693" s="3">
-        <v>15.5</v>
+        <v>15.04</v>
       </c>
       <c r="D693" s="3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="694" ht="15" customHeight="1" spans="1:4">
-      <c r="A694" s="4">
+      <c r="A694" s="2">
         <v>842</v>
       </c>
-      <c r="B694" s="4">
+      <c r="B694" s="2">
         <v>56</v>
       </c>
-      <c r="C694" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D694" s="5">
-        <v>6.9</v>
+      <c r="C694" s="3">
+        <v>15.05</v>
+      </c>
+      <c r="D694" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="695" ht="15" customHeight="1" spans="1:4">
@@ -10764,24 +10747,24 @@
         <v>56</v>
       </c>
       <c r="C695" s="3">
-        <v>15.5</v>
+        <v>15.07</v>
       </c>
       <c r="D695" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="696" ht="15" customHeight="1" spans="1:4">
-      <c r="A696" s="4">
+      <c r="A696" s="2">
         <v>844</v>
       </c>
-      <c r="B696" s="4">
+      <c r="B696" s="2">
         <v>56</v>
       </c>
-      <c r="C696" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D696" s="5">
-        <v>6</v>
+      <c r="C696" s="3">
+        <v>15.09</v>
+      </c>
+      <c r="D696" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="697" ht="15" customHeight="1" spans="1:4">
@@ -10792,23 +10775,23 @@
         <v>56</v>
       </c>
       <c r="C697" s="3">
-        <v>15.6</v>
+        <v>15.11</v>
       </c>
       <c r="D697" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="698" ht="15" customHeight="1" spans="1:4">
-      <c r="A698" s="4">
+      <c r="A698" s="2">
         <v>846</v>
       </c>
-      <c r="B698" s="4">
+      <c r="B698" s="2">
         <v>56</v>
       </c>
-      <c r="C698" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D698" s="5">
+      <c r="C698" s="3">
+        <v>15.13</v>
+      </c>
+      <c r="D698" s="3">
         <v>7</v>
       </c>
     </row>
@@ -10820,24 +10803,24 @@
         <v>56</v>
       </c>
       <c r="C699" s="3">
-        <v>15.6</v>
+        <v>15.15</v>
       </c>
       <c r="D699" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="700" ht="15" customHeight="1" spans="1:4">
-      <c r="A700" s="4">
+      <c r="A700" s="2">
         <v>848</v>
       </c>
-      <c r="B700" s="4">
+      <c r="B700" s="2">
         <v>56</v>
       </c>
-      <c r="C700" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D700" s="5">
-        <v>6.1</v>
+      <c r="C700" s="3">
+        <v>15.16</v>
+      </c>
+      <c r="D700" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="701" ht="15" customHeight="1" spans="1:4">
@@ -10848,24 +10831,24 @@
         <v>56</v>
       </c>
       <c r="C701" s="3">
-        <v>15.7</v>
+        <v>15.18</v>
       </c>
       <c r="D701" s="3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="702" ht="15" customHeight="1" spans="1:4">
-      <c r="A702" s="4">
+      <c r="A702" s="2">
         <v>850</v>
       </c>
-      <c r="B702" s="4">
+      <c r="B702" s="2">
         <v>56</v>
       </c>
-      <c r="C702" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D702" s="5">
-        <v>7.1</v>
+      <c r="C702" s="3">
+        <v>15.2</v>
+      </c>
+      <c r="D702" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="703" ht="15" customHeight="1" spans="1:4">
@@ -10876,24 +10859,24 @@
         <v>56</v>
       </c>
       <c r="C703" s="3">
-        <v>15.7</v>
+        <v>15.22</v>
       </c>
       <c r="D703" s="3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="704" ht="15" customHeight="1" spans="1:4">
-      <c r="A704" s="4">
+      <c r="A704" s="2">
         <v>852</v>
       </c>
-      <c r="B704" s="4">
+      <c r="B704" s="2">
         <v>56</v>
       </c>
-      <c r="C704" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D704" s="5">
-        <v>6.2</v>
+      <c r="C704" s="3">
+        <v>15.24</v>
+      </c>
+      <c r="D704" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="705" ht="15" customHeight="1" spans="1:4">
@@ -10904,24 +10887,24 @@
         <v>56</v>
       </c>
       <c r="C705" s="3">
-        <v>15.8</v>
+        <v>15.25</v>
       </c>
       <c r="D705" s="3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="706" ht="15" customHeight="1" spans="1:4">
-      <c r="A706" s="4">
+      <c r="A706" s="2">
         <v>854</v>
       </c>
-      <c r="B706" s="4">
+      <c r="B706" s="2">
         <v>56</v>
       </c>
-      <c r="C706" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D706" s="5">
-        <v>7.2</v>
+      <c r="C706" s="3">
+        <v>15.27</v>
+      </c>
+      <c r="D706" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="707" ht="15" customHeight="1" spans="1:4">
@@ -10932,24 +10915,24 @@
         <v>56</v>
       </c>
       <c r="C707" s="3">
-        <v>15.8</v>
+        <v>15.29</v>
       </c>
       <c r="D707" s="3">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="708" ht="15" customHeight="1" spans="1:4">
-      <c r="A708" s="4">
+      <c r="A708" s="2">
         <v>856</v>
       </c>
-      <c r="B708" s="4">
+      <c r="B708" s="2">
         <v>56</v>
       </c>
-      <c r="C708" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D708" s="5">
-        <v>6.3</v>
+      <c r="C708" s="3">
+        <v>15.31</v>
+      </c>
+      <c r="D708" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="709" ht="15" customHeight="1" spans="1:4">
@@ -10960,24 +10943,24 @@
         <v>56</v>
       </c>
       <c r="C709" s="3">
-        <v>15.9</v>
+        <v>15.33</v>
       </c>
       <c r="D709" s="3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="710" ht="15" customHeight="1" spans="1:4">
-      <c r="A710" s="4">
+      <c r="A710" s="2">
         <v>858</v>
       </c>
-      <c r="B710" s="4">
+      <c r="B710" s="2">
         <v>56</v>
       </c>
-      <c r="C710" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D710" s="5">
-        <v>7.3</v>
+      <c r="C710" s="3">
+        <v>15.35</v>
+      </c>
+      <c r="D710" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="711" ht="15" customHeight="1" spans="1:4">
@@ -10988,24 +10971,24 @@
         <v>56</v>
       </c>
       <c r="C711" s="3">
-        <v>15.9</v>
+        <v>15.36</v>
       </c>
       <c r="D711" s="3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="712" ht="15" customHeight="1" spans="1:4">
-      <c r="A712" s="4">
+      <c r="A712" s="2">
         <v>860</v>
       </c>
-      <c r="B712" s="4">
+      <c r="B712" s="2">
         <v>58</v>
       </c>
-      <c r="C712" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D712" s="5">
-        <v>5.9</v>
+      <c r="C712" s="3">
+        <v>14.84</v>
+      </c>
+      <c r="D712" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="713" ht="15" customHeight="1" spans="1:4">
@@ -11016,24 +10999,24 @@
         <v>58</v>
       </c>
       <c r="C713" s="3">
-        <v>15.4</v>
+        <v>14.86</v>
       </c>
       <c r="D713" s="3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="714" ht="15" customHeight="1" spans="1:4">
-      <c r="A714" s="4">
+      <c r="A714" s="2">
         <v>862</v>
       </c>
-      <c r="B714" s="4">
+      <c r="B714" s="2">
         <v>58</v>
       </c>
-      <c r="C714" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D714" s="5">
-        <v>6.9</v>
+      <c r="C714" s="3">
+        <v>14.88</v>
+      </c>
+      <c r="D714" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="715" ht="15" customHeight="1" spans="1:4">
@@ -11044,24 +11027,24 @@
         <v>58</v>
       </c>
       <c r="C715" s="3">
-        <v>15.4</v>
+        <v>14.89</v>
       </c>
       <c r="D715" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="716" ht="15" customHeight="1" spans="1:4">
-      <c r="A716" s="4">
+      <c r="A716" s="2">
         <v>864</v>
       </c>
-      <c r="B716" s="4">
+      <c r="B716" s="2">
         <v>58</v>
       </c>
-      <c r="C716" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D716" s="5">
-        <v>6</v>
+      <c r="C716" s="3">
+        <v>14.91</v>
+      </c>
+      <c r="D716" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="717" ht="15" customHeight="1" spans="1:4">
@@ -11072,24 +11055,24 @@
         <v>58</v>
       </c>
       <c r="C717" s="3">
-        <v>15.5</v>
+        <v>14.93</v>
       </c>
       <c r="D717" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="718" ht="15" customHeight="1" spans="1:4">
-      <c r="A718" s="4">
+      <c r="A718" s="2">
         <v>866</v>
       </c>
-      <c r="B718" s="4">
+      <c r="B718" s="2">
         <v>58</v>
       </c>
-      <c r="C718" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D718" s="5">
-        <v>7</v>
+      <c r="C718" s="3">
+        <v>15</v>
+      </c>
+      <c r="D718" s="3">
+        <v>5.5</v>
       </c>
     </row>
     <row r="719" ht="15" customHeight="1" spans="1:4">
@@ -11100,24 +11083,24 @@
         <v>58</v>
       </c>
       <c r="C719" s="3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D719" s="3">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="720" ht="15" customHeight="1" spans="1:4">
-      <c r="A720" s="4">
+      <c r="A720" s="2">
         <v>868</v>
       </c>
-      <c r="B720" s="4">
+      <c r="B720" s="2">
         <v>58</v>
       </c>
-      <c r="C720" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D720" s="5">
-        <v>6.1</v>
+      <c r="C720" s="3">
+        <v>15</v>
+      </c>
+      <c r="D720" s="3">
+        <v>6.5</v>
       </c>
     </row>
     <row r="721" ht="15" customHeight="1" spans="1:4">
@@ -11128,24 +11111,24 @@
         <v>58</v>
       </c>
       <c r="C721" s="3">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="D721" s="3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="722" ht="15" customHeight="1" spans="1:4">
-      <c r="A722" s="4">
+      <c r="A722" s="2">
         <v>870</v>
       </c>
-      <c r="B722" s="4">
+      <c r="B722" s="2">
         <v>58</v>
       </c>
-      <c r="C722" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D722" s="5">
-        <v>7.1</v>
+      <c r="C722" s="3">
+        <v>15.02</v>
+      </c>
+      <c r="D722" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="723" ht="15" customHeight="1" spans="1:4">
@@ -11156,24 +11139,24 @@
         <v>58</v>
       </c>
       <c r="C723" s="3">
-        <v>15.6</v>
+        <v>15.04</v>
       </c>
       <c r="D723" s="3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="724" ht="15" customHeight="1" spans="1:4">
-      <c r="A724" s="4">
+      <c r="A724" s="2">
         <v>872</v>
       </c>
-      <c r="B724" s="4">
+      <c r="B724" s="2">
         <v>58</v>
       </c>
-      <c r="C724" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D724" s="5">
-        <v>6.2</v>
+      <c r="C724" s="3">
+        <v>15.05</v>
+      </c>
+      <c r="D724" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="725" ht="15" customHeight="1" spans="1:4">
@@ -11184,24 +11167,24 @@
         <v>58</v>
       </c>
       <c r="C725" s="3">
-        <v>15.6</v>
+        <v>15.07</v>
       </c>
       <c r="D725" s="3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="726" ht="15" customHeight="1" spans="1:4">
-      <c r="A726" s="4">
+      <c r="A726" s="2">
         <v>874</v>
       </c>
-      <c r="B726" s="4">
+      <c r="B726" s="2">
         <v>58</v>
       </c>
-      <c r="C726" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D726" s="5">
-        <v>7.2</v>
+      <c r="C726" s="3">
+        <v>15.09</v>
+      </c>
+      <c r="D726" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="727" ht="15" customHeight="1" spans="1:4">
@@ -11212,24 +11195,24 @@
         <v>58</v>
       </c>
       <c r="C727" s="3">
-        <v>15.6</v>
+        <v>15.11</v>
       </c>
       <c r="D727" s="3">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="728" ht="15" customHeight="1" spans="1:4">
-      <c r="A728" s="4">
+      <c r="A728" s="2">
         <v>876</v>
       </c>
-      <c r="B728" s="4">
+      <c r="B728" s="2">
         <v>58</v>
       </c>
-      <c r="C728" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D728" s="5">
-        <v>7.2</v>
+      <c r="C728" s="3">
+        <v>15.12</v>
+      </c>
+      <c r="D728" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="729" ht="15" customHeight="1" spans="1:4">
@@ -11240,24 +11223,24 @@
         <v>58</v>
       </c>
       <c r="C729" s="3">
-        <v>15.6</v>
+        <v>15.14</v>
       </c>
       <c r="D729" s="3">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="730" ht="15" customHeight="1" spans="1:4">
-      <c r="A730" s="4">
+      <c r="A730" s="2">
         <v>878</v>
       </c>
-      <c r="B730" s="4">
+      <c r="B730" s="2">
         <v>58</v>
       </c>
-      <c r="C730" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D730" s="5">
-        <v>6.3</v>
+      <c r="C730" s="3">
+        <v>15.16</v>
+      </c>
+      <c r="D730" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="731" ht="15" customHeight="1" spans="1:4">
@@ -11268,24 +11251,24 @@
         <v>58</v>
       </c>
       <c r="C731" s="3">
-        <v>15.7</v>
+        <v>15.18</v>
       </c>
       <c r="D731" s="3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="732" ht="15" customHeight="1" spans="1:4">
-      <c r="A732" s="4">
+      <c r="A732" s="2">
         <v>880</v>
       </c>
-      <c r="B732" s="4">
+      <c r="B732" s="2">
         <v>58</v>
       </c>
-      <c r="C732" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D732" s="5">
-        <v>7.3</v>
+      <c r="C732" s="3">
+        <v>15.19</v>
+      </c>
+      <c r="D732" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="733" ht="15" customHeight="1" spans="1:4">
@@ -11296,24 +11279,24 @@
         <v>58</v>
       </c>
       <c r="C733" s="3">
-        <v>15.7</v>
+        <v>15.21</v>
       </c>
       <c r="D733" s="3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="734" ht="15" customHeight="1" spans="1:4">
-      <c r="A734" s="4">
+      <c r="A734" s="2">
         <v>882</v>
       </c>
-      <c r="B734" s="4">
+      <c r="B734" s="2">
         <v>58</v>
       </c>
-      <c r="C734" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D734" s="5">
-        <v>6.4</v>
+      <c r="C734" s="3">
+        <v>15.23</v>
+      </c>
+      <c r="D734" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="735" ht="15" customHeight="1" spans="1:4">
@@ -11324,24 +11307,24 @@
         <v>58</v>
       </c>
       <c r="C735" s="3">
-        <v>15.8</v>
+        <v>15.25</v>
       </c>
       <c r="D735" s="3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="736" ht="15" customHeight="1" spans="1:4">
-      <c r="A736" s="4">
+      <c r="A736" s="2">
         <v>884</v>
       </c>
-      <c r="B736" s="4">
+      <c r="B736" s="2">
         <v>58</v>
       </c>
-      <c r="C736" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D736" s="5">
-        <v>7.4</v>
+      <c r="C736" s="3">
+        <v>15.26</v>
+      </c>
+      <c r="D736" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="737" ht="15" customHeight="1" spans="1:4">
@@ -11352,24 +11335,24 @@
         <v>58</v>
       </c>
       <c r="C737" s="3">
-        <v>15.8</v>
+        <v>15.28</v>
       </c>
       <c r="D737" s="3">
-        <v>7.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="738" ht="15" customHeight="1" spans="1:4">
-      <c r="A738" s="4">
+      <c r="A738" s="2">
         <v>886</v>
       </c>
-      <c r="B738" s="4">
+      <c r="B738" s="2">
         <v>60</v>
       </c>
-      <c r="C738" s="5">
-        <v>15.3</v>
-      </c>
-      <c r="D738" s="5">
-        <v>5.9</v>
+      <c r="C738" s="3">
+        <v>14.78</v>
+      </c>
+      <c r="D738" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="739" ht="15" customHeight="1" spans="1:4">
@@ -11380,24 +11363,24 @@
         <v>60</v>
       </c>
       <c r="C739" s="3">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="D739" s="3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="740" ht="15" customHeight="1" spans="1:4">
-      <c r="A740" s="4">
+      <c r="A740" s="2">
         <v>888</v>
       </c>
-      <c r="B740" s="4">
+      <c r="B740" s="2">
         <v>60</v>
       </c>
-      <c r="C740" s="5">
-        <v>15.3</v>
-      </c>
-      <c r="D740" s="5">
-        <v>6.9</v>
+      <c r="C740" s="3">
+        <v>14.81</v>
+      </c>
+      <c r="D740" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="741" ht="15" customHeight="1" spans="1:4">
@@ -11408,24 +11391,24 @@
         <v>60</v>
       </c>
       <c r="C741" s="3">
-        <v>15.3</v>
+        <v>14.83</v>
       </c>
       <c r="D741" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="742" ht="15" customHeight="1" spans="1:4">
-      <c r="A742" s="4">
+      <c r="A742" s="2">
         <v>890</v>
       </c>
-      <c r="B742" s="4">
+      <c r="B742" s="2">
         <v>60</v>
       </c>
-      <c r="C742" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D742" s="5">
-        <v>6</v>
+      <c r="C742" s="3">
+        <v>14.85</v>
+      </c>
+      <c r="D742" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="743" ht="15" customHeight="1" spans="1:4">
@@ -11436,23 +11419,23 @@
         <v>60</v>
       </c>
       <c r="C743" s="3">
-        <v>15.4</v>
+        <v>14.86</v>
       </c>
       <c r="D743" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="744" ht="15" customHeight="1" spans="1:4">
-      <c r="A744" s="4">
+      <c r="A744" s="2">
         <v>892</v>
       </c>
-      <c r="B744" s="4">
+      <c r="B744" s="2">
         <v>60</v>
       </c>
-      <c r="C744" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D744" s="5">
+      <c r="C744" s="3">
+        <v>14.88</v>
+      </c>
+      <c r="D744" s="3">
         <v>7</v>
       </c>
     </row>
@@ -11464,24 +11447,24 @@
         <v>60</v>
       </c>
       <c r="C745" s="3">
-        <v>15.4</v>
+        <v>14.9</v>
       </c>
       <c r="D745" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="746" ht="15" customHeight="1" spans="1:4">
-      <c r="A746" s="4">
+      <c r="A746" s="2">
         <v>894</v>
       </c>
-      <c r="B746" s="4">
+      <c r="B746" s="2">
         <v>60</v>
       </c>
-      <c r="C746" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D746" s="5">
-        <v>6.1</v>
+      <c r="C746" s="3">
+        <v>14.92</v>
+      </c>
+      <c r="D746" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="747" ht="15" customHeight="1" spans="1:4">
@@ -11492,24 +11475,24 @@
         <v>60</v>
       </c>
       <c r="C747" s="3">
-        <v>15.5</v>
+        <v>14.93</v>
       </c>
       <c r="D747" s="3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="748" ht="15" customHeight="1" spans="1:4">
-      <c r="A748" s="4">
+      <c r="A748" s="2">
         <v>896</v>
       </c>
-      <c r="B748" s="4">
+      <c r="B748" s="2">
         <v>60</v>
       </c>
-      <c r="C748" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D748" s="5">
-        <v>7.1</v>
+      <c r="C748" s="3">
+        <v>15</v>
+      </c>
+      <c r="D748" s="3">
+        <v>5.5</v>
       </c>
     </row>
     <row r="749" ht="15" customHeight="1" spans="1:4">
@@ -11520,24 +11503,24 @@
         <v>60</v>
       </c>
       <c r="C749" s="3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D749" s="3">
-        <v>7.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="750" ht="15" customHeight="1" spans="1:4">
-      <c r="A750" s="4">
+      <c r="A750" s="2">
         <v>898</v>
       </c>
-      <c r="B750" s="4">
+      <c r="B750" s="2">
         <v>60</v>
       </c>
-      <c r="C750" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D750" s="5">
-        <v>6.2</v>
+      <c r="C750" s="3">
+        <v>15</v>
+      </c>
+      <c r="D750" s="3">
+        <v>6.5</v>
       </c>
     </row>
     <row r="751" ht="15" customHeight="1" spans="1:4">
@@ -11548,24 +11531,24 @@
         <v>60</v>
       </c>
       <c r="C751" s="3">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="D751" s="3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="752" ht="15" customHeight="1" spans="1:4">
-      <c r="A752" s="4">
+      <c r="A752" s="2">
         <v>900</v>
       </c>
-      <c r="B752" s="4">
+      <c r="B752" s="2">
         <v>60</v>
       </c>
-      <c r="C752" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D752" s="5">
-        <v>7.2</v>
+      <c r="C752" s="3">
+        <v>15.02</v>
+      </c>
+      <c r="D752" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="753" ht="15" customHeight="1" spans="1:4">
@@ -11576,24 +11559,24 @@
         <v>60</v>
       </c>
       <c r="C753" s="3">
-        <v>15.6</v>
+        <v>15.03</v>
       </c>
       <c r="D753" s="3">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="754" ht="15" customHeight="1" spans="1:4">
-      <c r="A754" s="4">
+      <c r="A754" s="2">
         <v>902</v>
       </c>
-      <c r="B754" s="4">
+      <c r="B754" s="2">
         <v>60</v>
       </c>
-      <c r="C754" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D754" s="5">
-        <v>6.3</v>
+      <c r="C754" s="3">
+        <v>15.05</v>
+      </c>
+      <c r="D754" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="755" ht="15" customHeight="1" spans="1:4">
@@ -11604,24 +11587,24 @@
         <v>60</v>
       </c>
       <c r="C755" s="3">
-        <v>15.7</v>
+        <v>15.07</v>
       </c>
       <c r="D755" s="3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="756" ht="15" customHeight="1" spans="1:4">
-      <c r="A756" s="4">
+      <c r="A756" s="2">
         <v>904</v>
       </c>
-      <c r="B756" s="4">
+      <c r="B756" s="2">
         <v>60</v>
       </c>
-      <c r="C756" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D756" s="5">
-        <v>7.3</v>
+      <c r="C756" s="3">
+        <v>15.08</v>
+      </c>
+      <c r="D756" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="757" ht="15" customHeight="1" spans="1:4">
@@ -11632,24 +11615,24 @@
         <v>60</v>
       </c>
       <c r="C757" s="3">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="D757" s="3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="758" ht="15" customHeight="1" spans="1:4">
-      <c r="A758" s="4">
+      <c r="A758" s="2">
         <v>906</v>
       </c>
-      <c r="B758" s="4">
+      <c r="B758" s="2">
         <v>60</v>
       </c>
-      <c r="C758" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D758" s="5">
-        <v>6.4</v>
+      <c r="C758" s="3">
+        <v>15.12</v>
+      </c>
+      <c r="D758" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="759" ht="15" customHeight="1" spans="1:4">
@@ -11660,24 +11643,24 @@
         <v>60</v>
       </c>
       <c r="C759" s="3">
-        <v>15.8</v>
+        <v>15.14</v>
       </c>
       <c r="D759" s="3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="760" ht="15" customHeight="1" spans="1:4">
-      <c r="A760" s="4">
+      <c r="A760" s="2">
         <v>908</v>
       </c>
-      <c r="B760" s="4">
+      <c r="B760" s="2">
         <v>60</v>
       </c>
-      <c r="C760" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D760" s="5">
-        <v>7.4</v>
+      <c r="C760" s="3">
+        <v>15.15</v>
+      </c>
+      <c r="D760" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="761" ht="15" customHeight="1" spans="1:4">
@@ -11688,24 +11671,24 @@
         <v>60</v>
       </c>
       <c r="C761" s="3">
-        <v>15.8</v>
+        <v>15.17</v>
       </c>
       <c r="D761" s="3">
-        <v>7.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="762" ht="15" customHeight="1" spans="1:4">
-      <c r="A762" s="4">
+      <c r="A762" s="2">
         <v>910</v>
       </c>
-      <c r="B762" s="4">
+      <c r="B762" s="2">
         <v>62</v>
       </c>
-      <c r="C762" s="5">
-        <v>15.3</v>
-      </c>
-      <c r="D762" s="5">
-        <v>6</v>
+      <c r="C762" s="3">
+        <v>14.69</v>
+      </c>
+      <c r="D762" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="763" ht="15" customHeight="1" spans="1:4">
@@ -11716,23 +11699,23 @@
         <v>62</v>
       </c>
       <c r="C763" s="3">
-        <v>15.3</v>
+        <v>14.7</v>
       </c>
       <c r="D763" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="764" ht="15" customHeight="1" spans="1:4">
-      <c r="A764" s="4">
+      <c r="A764" s="2">
         <v>912</v>
       </c>
-      <c r="B764" s="4">
+      <c r="B764" s="2">
         <v>62</v>
       </c>
-      <c r="C764" s="5">
-        <v>15.3</v>
-      </c>
-      <c r="D764" s="5">
+      <c r="C764" s="3">
+        <v>14.72</v>
+      </c>
+      <c r="D764" s="3">
         <v>7</v>
       </c>
     </row>
@@ -11744,24 +11727,24 @@
         <v>62</v>
       </c>
       <c r="C765" s="3">
-        <v>15.3</v>
+        <v>14.74</v>
       </c>
       <c r="D765" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="766" ht="15" customHeight="1" spans="1:4">
-      <c r="A766" s="4">
+      <c r="A766" s="2">
         <v>914</v>
       </c>
-      <c r="B766" s="4">
+      <c r="B766" s="2">
         <v>62</v>
       </c>
-      <c r="C766" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D766" s="5">
-        <v>6.1</v>
+      <c r="C766" s="3">
+        <v>14.75</v>
+      </c>
+      <c r="D766" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="767" ht="15" customHeight="1" spans="1:4">
@@ -11772,24 +11755,24 @@
         <v>62</v>
       </c>
       <c r="C767" s="3">
-        <v>15.4</v>
+        <v>14.77</v>
       </c>
       <c r="D767" s="3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="768" ht="15" customHeight="1" spans="1:4">
-      <c r="A768" s="4">
+      <c r="A768" s="2">
         <v>916</v>
       </c>
-      <c r="B768" s="4">
+      <c r="B768" s="2">
         <v>62</v>
       </c>
-      <c r="C768" s="5">
-        <v>15.4</v>
-      </c>
-      <c r="D768" s="5">
-        <v>7.1</v>
+      <c r="C768" s="3">
+        <v>14.79</v>
+      </c>
+      <c r="D768" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="769" ht="15" customHeight="1" spans="1:4">
@@ -11800,24 +11783,24 @@
         <v>62</v>
       </c>
       <c r="C769" s="3">
-        <v>15.4</v>
+        <v>14.8</v>
       </c>
       <c r="D769" s="3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="770" ht="15" customHeight="1" spans="1:4">
-      <c r="A770" s="4">
+      <c r="A770" s="2">
         <v>918</v>
       </c>
-      <c r="B770" s="4">
+      <c r="B770" s="2">
         <v>62</v>
       </c>
-      <c r="C770" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D770" s="5">
-        <v>6.2</v>
+      <c r="C770" s="3">
+        <v>14.82</v>
+      </c>
+      <c r="D770" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="771" ht="15" customHeight="1" spans="1:4">
@@ -11828,24 +11811,24 @@
         <v>62</v>
       </c>
       <c r="C771" s="3">
-        <v>15.5</v>
+        <v>14.84</v>
       </c>
       <c r="D771" s="3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="772" ht="15" customHeight="1" spans="1:4">
-      <c r="A772" s="4">
+      <c r="A772" s="2">
         <v>920</v>
       </c>
-      <c r="B772" s="4">
+      <c r="B772" s="2">
         <v>62</v>
       </c>
-      <c r="C772" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D772" s="5">
-        <v>7.2</v>
+      <c r="C772" s="3">
+        <v>14.85</v>
+      </c>
+      <c r="D772" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="773" ht="15" customHeight="1" spans="1:4">
@@ -11856,24 +11839,24 @@
         <v>62</v>
       </c>
       <c r="C773" s="3">
-        <v>15.5</v>
+        <v>14.87</v>
       </c>
       <c r="D773" s="3">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="774" ht="15" customHeight="1" spans="1:4">
-      <c r="A774" s="4">
+      <c r="A774" s="2">
         <v>922</v>
       </c>
-      <c r="B774" s="4">
+      <c r="B774" s="2">
         <v>62</v>
       </c>
-      <c r="C774" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D774" s="5">
-        <v>6.3</v>
+      <c r="C774" s="3">
+        <v>14.89</v>
+      </c>
+      <c r="D774" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="775" ht="15" customHeight="1" spans="1:4">
@@ -11884,24 +11867,24 @@
         <v>62</v>
       </c>
       <c r="C775" s="3">
-        <v>15.5</v>
+        <v>14.9</v>
       </c>
       <c r="D775" s="3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="776" ht="15" customHeight="1" spans="1:4">
-      <c r="A776" s="4">
+      <c r="A776" s="2">
         <v>924</v>
       </c>
-      <c r="B776" s="4">
+      <c r="B776" s="2">
         <v>62</v>
       </c>
-      <c r="C776" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D776" s="5">
-        <v>7.3</v>
+      <c r="C776" s="3">
+        <v>14.92</v>
+      </c>
+      <c r="D776" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="777" ht="15" customHeight="1" spans="1:4">
@@ -11912,24 +11895,24 @@
         <v>62</v>
       </c>
       <c r="C777" s="3">
-        <v>15.5</v>
+        <v>14.93</v>
       </c>
       <c r="D777" s="3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="778" ht="15" customHeight="1" spans="1:4">
-      <c r="A778" s="4">
+      <c r="A778" s="2">
         <v>926</v>
       </c>
-      <c r="B778" s="4">
+      <c r="B778" s="2">
         <v>62</v>
       </c>
-      <c r="C778" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D778" s="5">
-        <v>6.8</v>
+      <c r="C778" s="3">
+        <v>15</v>
+      </c>
+      <c r="D778" s="3">
+        <v>5.5</v>
       </c>
     </row>
     <row r="779" ht="15" customHeight="1" spans="1:4">
@@ -11940,24 +11923,24 @@
         <v>62</v>
       </c>
       <c r="C779" s="3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="D779" s="3">
-        <v>7.3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="780" ht="15" customHeight="1" spans="1:4">
-      <c r="A780" s="4">
+      <c r="A780" s="2">
         <v>928</v>
       </c>
-      <c r="B780" s="4">
+      <c r="B780" s="2">
         <v>62</v>
       </c>
-      <c r="C780" s="5">
-        <v>15.5</v>
-      </c>
-      <c r="D780" s="5">
-        <v>7.8</v>
+      <c r="C780" s="3">
+        <v>15</v>
+      </c>
+      <c r="D780" s="3">
+        <v>6.5</v>
       </c>
     </row>
     <row r="781" ht="15" customHeight="1" spans="1:4">
@@ -11968,24 +11951,24 @@
         <v>62</v>
       </c>
       <c r="C781" s="3">
-        <v>15.6</v>
+        <v>15</v>
       </c>
       <c r="D781" s="3">
-        <v>6.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="782" ht="15" customHeight="1" spans="1:4">
-      <c r="A782" s="4">
+      <c r="A782" s="2">
         <v>930</v>
       </c>
-      <c r="B782" s="4">
+      <c r="B782" s="2">
         <v>62</v>
       </c>
-      <c r="C782" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D782" s="5">
-        <v>6.9</v>
+      <c r="C782" s="3">
+        <v>15.02</v>
+      </c>
+      <c r="D782" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="783" ht="15" customHeight="1" spans="1:4">
@@ -11996,24 +11979,24 @@
         <v>62</v>
       </c>
       <c r="C783" s="3">
-        <v>15.6</v>
+        <v>15.03</v>
       </c>
       <c r="D783" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="784" ht="15" customHeight="1" spans="1:4">
-      <c r="A784" s="4">
+      <c r="A784" s="2">
         <v>932</v>
       </c>
-      <c r="B784" s="4">
+      <c r="B784" s="2">
         <v>62</v>
       </c>
-      <c r="C784" s="5">
-        <v>15.6</v>
-      </c>
-      <c r="D784" s="5">
-        <v>7.9</v>
+      <c r="C784" s="3">
+        <v>15.05</v>
+      </c>
+      <c r="D784" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="785" ht="15" customHeight="1" spans="1:4">
@@ -12024,23 +12007,23 @@
         <v>62</v>
       </c>
       <c r="C785" s="3">
-        <v>15.7</v>
+        <v>15.07</v>
       </c>
       <c r="D785" s="3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="786" ht="15" customHeight="1" spans="1:4">
-      <c r="A786" s="4">
+      <c r="A786" s="2">
         <v>934</v>
       </c>
-      <c r="B786" s="4">
+      <c r="B786" s="2">
         <v>62</v>
       </c>
-      <c r="C786" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D786" s="5">
+      <c r="C786" s="3">
+        <v>15.08</v>
+      </c>
+      <c r="D786" s="3">
         <v>7</v>
       </c>
     </row>
@@ -12052,24 +12035,24 @@
         <v>62</v>
       </c>
       <c r="C787" s="3">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="D787" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="788" ht="15" customHeight="1" spans="1:4">
-      <c r="A788" s="4">
+      <c r="A788" s="2">
         <v>936</v>
       </c>
-      <c r="B788" s="4">
+      <c r="B788" s="2">
         <v>62</v>
       </c>
-      <c r="C788" s="5">
-        <v>15.7</v>
-      </c>
-      <c r="D788" s="5">
-        <v>8</v>
+      <c r="C788" s="3">
+        <v>15.11</v>
+      </c>
+      <c r="D788" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="789" ht="15" customHeight="1" spans="1:4">
@@ -12080,24 +12063,24 @@
         <v>62</v>
       </c>
       <c r="C789" s="3">
-        <v>15.8</v>
+        <v>15.13</v>
       </c>
       <c r="D789" s="3">
-        <v>6.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="790" ht="15" customHeight="1" spans="1:4">
-      <c r="A790" s="4">
+      <c r="A790" s="2">
         <v>938</v>
       </c>
-      <c r="B790" s="4">
+      <c r="B790" s="2">
         <v>62</v>
       </c>
-      <c r="C790" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D790" s="5">
-        <v>7.1</v>
+      <c r="C790" s="3">
+        <v>15.15</v>
+      </c>
+      <c r="D790" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="791" ht="15" customHeight="1" spans="1:4">
@@ -12108,24 +12091,24 @@
         <v>62</v>
       </c>
       <c r="C791" s="3">
-        <v>15.8</v>
+        <v>15.16</v>
       </c>
       <c r="D791" s="3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="792" ht="15" customHeight="1" spans="1:4">
-      <c r="A792" s="4">
+      <c r="A792" s="2">
         <v>940</v>
       </c>
-      <c r="B792" s="4">
+      <c r="B792" s="2">
         <v>62</v>
       </c>
-      <c r="C792" s="5">
-        <v>15.8</v>
-      </c>
-      <c r="D792" s="5">
-        <v>8.1</v>
+      <c r="C792" s="3">
+        <v>15.18</v>
+      </c>
+      <c r="D792" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="793" ht="15" customHeight="1" spans="1:4">
@@ -12136,24 +12119,24 @@
         <v>62</v>
       </c>
       <c r="C793" s="3">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="D793" s="3">
-        <v>6.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="794" ht="15" customHeight="1" spans="1:4">
-      <c r="A794" s="4">
+      <c r="A794" s="2">
         <v>942</v>
       </c>
-      <c r="B794" s="4">
+      <c r="B794" s="2">
         <v>62</v>
       </c>
-      <c r="C794" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D794" s="5">
-        <v>7.2</v>
+      <c r="C794" s="3">
+        <v>15.21</v>
+      </c>
+      <c r="D794" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="795" ht="15" customHeight="1" spans="1:4">
@@ -12164,24 +12147,24 @@
         <v>62</v>
       </c>
       <c r="C795" s="3">
-        <v>15.9</v>
+        <v>15.23</v>
       </c>
       <c r="D795" s="3">
-        <v>7.7</v>
+        <v>7</v>
       </c>
     </row>
     <row r="796" ht="15" customHeight="1" spans="1:4">
-      <c r="A796" s="4">
+      <c r="A796" s="2">
         <v>944</v>
       </c>
-      <c r="B796" s="4">
+      <c r="B796" s="2">
         <v>62</v>
       </c>
-      <c r="C796" s="5">
-        <v>15.9</v>
-      </c>
-      <c r="D796" s="5">
-        <v>8.2</v>
+      <c r="C796" s="3">
+        <v>15.25</v>
+      </c>
+      <c r="D796" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="797" ht="15" customHeight="1" spans="1:4">
@@ -12192,24 +12175,24 @@
         <v>62</v>
       </c>
       <c r="C797" s="3">
-        <v>16</v>
+        <v>15.26</v>
       </c>
       <c r="D797" s="3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="798" ht="15" customHeight="1" spans="1:4">
-      <c r="A798" s="4">
+      <c r="A798" s="2">
         <v>946</v>
       </c>
-      <c r="B798" s="4">
+      <c r="B798" s="2">
         <v>62</v>
       </c>
-      <c r="C798" s="5">
-        <v>16</v>
-      </c>
-      <c r="D798" s="5">
-        <v>7.3</v>
+      <c r="C798" s="3">
+        <v>15.28</v>
+      </c>
+      <c r="D798" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="799" ht="15" customHeight="1" spans="1:4">
@@ -12220,24 +12203,24 @@
         <v>62</v>
       </c>
       <c r="C799" s="3">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="D799" s="3">
-        <v>7.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="800" ht="15" customHeight="1" spans="1:4">
-      <c r="A800" s="4">
+      <c r="A800" s="2">
         <v>948</v>
       </c>
-      <c r="B800" s="4">
+      <c r="B800" s="2">
         <v>62</v>
       </c>
-      <c r="C800" s="5">
-        <v>16</v>
-      </c>
-      <c r="D800" s="5">
-        <v>8.3</v>
+      <c r="C800" s="3">
+        <v>15.31</v>
+      </c>
+      <c r="D800" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="801" ht="15" customHeight="1" spans="1:4">
@@ -12248,24 +12231,24 @@
         <v>62</v>
       </c>
       <c r="C801" s="3">
-        <v>16.1</v>
+        <v>15.33</v>
       </c>
       <c r="D801" s="3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="802" ht="15" customHeight="1" spans="1:4">
-      <c r="A802" s="4">
+      <c r="A802" s="2">
         <v>950</v>
       </c>
-      <c r="B802" s="4">
+      <c r="B802" s="2">
         <v>62</v>
       </c>
-      <c r="C802" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D802" s="5">
-        <v>7.4</v>
+      <c r="C802" s="3">
+        <v>15.34</v>
+      </c>
+      <c r="D802" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="803" ht="15" customHeight="1" spans="1:4">
@@ -12276,24 +12259,24 @@
         <v>62</v>
       </c>
       <c r="C803" s="3">
-        <v>16.1</v>
+        <v>15.36</v>
       </c>
       <c r="D803" s="3">
-        <v>7.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="804" ht="15" customHeight="1" spans="1:4">
-      <c r="A804" s="4">
+      <c r="A804" s="2">
         <v>952</v>
       </c>
-      <c r="B804" s="4">
+      <c r="B804" s="2">
         <v>62</v>
       </c>
-      <c r="C804" s="5">
-        <v>16.1</v>
-      </c>
-      <c r="D804" s="5">
-        <v>8.4</v>
+      <c r="C804" s="3">
+        <v>15.38</v>
+      </c>
+      <c r="D804" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="805" ht="15" customHeight="1" spans="1:4">
@@ -12304,24 +12287,24 @@
         <v>62</v>
       </c>
       <c r="C805" s="3">
-        <v>16.2</v>
+        <v>15.39</v>
       </c>
       <c r="D805" s="3">
         <v>7</v>
       </c>
     </row>
     <row r="806" ht="15" customHeight="1" spans="1:4">
-      <c r="A806" s="4">
+      <c r="A806" s="2">
         <v>954</v>
       </c>
-      <c r="B806" s="4">
+      <c r="B806" s="2">
         <v>62</v>
       </c>
-      <c r="C806" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="D806" s="5">
-        <v>7.5</v>
+      <c r="C806" s="3">
+        <v>15.41</v>
+      </c>
+      <c r="D806" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="807" ht="15" customHeight="1" spans="1:4">
@@ -12332,24 +12315,24 @@
         <v>62</v>
       </c>
       <c r="C807" s="3">
-        <v>16.2</v>
+        <v>15.43</v>
       </c>
       <c r="D807" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="808" ht="15" customHeight="1" spans="1:4">
-      <c r="A808" s="4">
+      <c r="A808" s="2">
         <v>956</v>
       </c>
-      <c r="B808" s="4">
+      <c r="B808" s="2">
         <v>62</v>
       </c>
-      <c r="C808" s="5">
-        <v>16.2</v>
-      </c>
-      <c r="D808" s="5">
-        <v>8.5</v>
+      <c r="C808" s="3">
+        <v>15.44</v>
+      </c>
+      <c r="D808" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="809" ht="15" customHeight="1" spans="1:4">
@@ -12360,24 +12343,24 @@
         <v>62</v>
       </c>
       <c r="C809" s="3">
-        <v>16.3</v>
+        <v>15.46</v>
       </c>
       <c r="D809" s="3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="810" ht="15" customHeight="1" spans="1:4">
-      <c r="A810" s="4">
+      <c r="A810" s="2">
         <v>958</v>
       </c>
-      <c r="B810" s="4">
+      <c r="B810" s="2">
         <v>62</v>
       </c>
-      <c r="C810" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D810" s="5">
-        <v>7.6</v>
+      <c r="C810" s="3">
+        <v>15.48</v>
+      </c>
+      <c r="D810" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="811" ht="15" customHeight="1" spans="1:4">
@@ -12388,24 +12371,24 @@
         <v>62</v>
       </c>
       <c r="C811" s="3">
-        <v>16.3</v>
+        <v>15.49</v>
       </c>
       <c r="D811" s="3">
-        <v>8.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="812" ht="15" customHeight="1" spans="1:4">
-      <c r="A812" s="4">
+      <c r="A812" s="2">
         <v>960</v>
       </c>
-      <c r="B812" s="4">
+      <c r="B812" s="2">
         <v>62</v>
       </c>
-      <c r="C812" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D812" s="5">
-        <v>8.6</v>
+      <c r="C812" s="3">
+        <v>15.51</v>
+      </c>
+      <c r="D812" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="813" ht="15" customHeight="1" spans="1:4">
@@ -12416,24 +12399,24 @@
         <v>62</v>
       </c>
       <c r="C813" s="3">
-        <v>16.3</v>
+        <v>15.52</v>
       </c>
       <c r="D813" s="3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="814" ht="15" customHeight="1" spans="1:4">
-      <c r="A814" s="4">
+      <c r="A814" s="2">
         <v>962</v>
       </c>
-      <c r="B814" s="4">
+      <c r="B814" s="2">
         <v>62</v>
       </c>
-      <c r="C814" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D814" s="5">
-        <v>7.7</v>
+      <c r="C814" s="3">
+        <v>15.54</v>
+      </c>
+      <c r="D814" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="815" ht="15" customHeight="1" spans="1:4">
@@ -12444,24 +12427,24 @@
         <v>62</v>
       </c>
       <c r="C815" s="3">
-        <v>16.3</v>
+        <v>15.56</v>
       </c>
       <c r="D815" s="3">
-        <v>8.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="816" ht="15" customHeight="1" spans="1:4">
-      <c r="A816" s="4">
+      <c r="A816" s="2">
         <v>964</v>
       </c>
-      <c r="B816" s="4">
+      <c r="B816" s="2">
         <v>62</v>
       </c>
-      <c r="C816" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D816" s="5">
-        <v>8.7</v>
+      <c r="C816" s="3">
+        <v>15.57</v>
+      </c>
+      <c r="D816" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="817" ht="15" customHeight="1" spans="1:4">
@@ -12472,24 +12455,24 @@
         <v>62</v>
       </c>
       <c r="C817" s="3">
-        <v>16.4</v>
+        <v>15.59</v>
       </c>
       <c r="D817" s="3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="818" ht="15" customHeight="1" spans="1:4">
-      <c r="A818" s="4">
+      <c r="A818" s="2">
         <v>966</v>
       </c>
-      <c r="B818" s="4">
+      <c r="B818" s="2">
         <v>62</v>
       </c>
-      <c r="C818" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D818" s="5">
-        <v>7.8</v>
+      <c r="C818" s="3">
+        <v>15.61</v>
+      </c>
+      <c r="D818" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="819" ht="15" customHeight="1" spans="1:4">
@@ -12500,24 +12483,24 @@
         <v>62</v>
       </c>
       <c r="C819" s="3">
-        <v>16.4</v>
+        <v>15.62</v>
       </c>
       <c r="D819" s="3">
-        <v>8.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="820" ht="15" customHeight="1" spans="1:4">
-      <c r="A820" s="4">
+      <c r="A820" s="2">
         <v>968</v>
       </c>
-      <c r="B820" s="4">
+      <c r="B820" s="2">
         <v>62</v>
       </c>
-      <c r="C820" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D820" s="5">
-        <v>8.8</v>
+      <c r="C820" s="3">
+        <v>15.64</v>
+      </c>
+      <c r="D820" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="821" ht="15" customHeight="1" spans="1:4">
@@ -12528,24 +12511,24 @@
         <v>62</v>
       </c>
       <c r="C821" s="3">
-        <v>16.4</v>
+        <v>15.66</v>
       </c>
       <c r="D821" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="822" ht="15" customHeight="1" spans="1:4">
-      <c r="A822" s="4">
+      <c r="A822" s="2">
         <v>970</v>
       </c>
-      <c r="B822" s="4">
+      <c r="B822" s="2">
         <v>62</v>
       </c>
-      <c r="C822" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D822" s="5">
-        <v>7.9</v>
+      <c r="C822" s="3">
+        <v>15.67</v>
+      </c>
+      <c r="D822" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="823" ht="15" customHeight="1" spans="1:4">
@@ -12556,24 +12539,24 @@
         <v>62</v>
       </c>
       <c r="C823" s="3">
-        <v>16.4</v>
+        <v>15.69</v>
       </c>
       <c r="D823" s="3">
-        <v>8.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="824" ht="15" customHeight="1" spans="1:4">
-      <c r="A824" s="4">
+      <c r="A824" s="2">
         <v>972</v>
       </c>
-      <c r="B824" s="4">
+      <c r="B824" s="2">
         <v>62</v>
       </c>
-      <c r="C824" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D824" s="5">
-        <v>8.9</v>
+      <c r="C824" s="3">
+        <v>15.7</v>
+      </c>
+      <c r="D824" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="825" ht="15" customHeight="1" spans="1:4">
@@ -12584,24 +12567,24 @@
         <v>62</v>
       </c>
       <c r="C825" s="3">
-        <v>16.4</v>
+        <v>15.72</v>
       </c>
       <c r="D825" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="826" ht="15" customHeight="1" spans="1:4">
-      <c r="A826" s="4">
+      <c r="A826" s="2">
         <v>974</v>
       </c>
-      <c r="B826" s="4">
+      <c r="B826" s="2">
         <v>62</v>
       </c>
-      <c r="C826" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D826" s="5">
-        <v>8</v>
+      <c r="C826" s="3">
+        <v>15.74</v>
+      </c>
+      <c r="D826" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="827" ht="15" customHeight="1" spans="1:4">
@@ -12612,24 +12595,24 @@
         <v>62</v>
       </c>
       <c r="C827" s="3">
-        <v>16.4</v>
+        <v>15.75</v>
       </c>
       <c r="D827" s="3">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="828" ht="15" customHeight="1" spans="1:4">
-      <c r="A828" s="4">
+      <c r="A828" s="2">
         <v>976</v>
       </c>
-      <c r="B828" s="4">
+      <c r="B828" s="2">
         <v>62</v>
       </c>
-      <c r="C828" s="5">
-        <v>16.3</v>
-      </c>
-      <c r="D828" s="5">
-        <v>7.5</v>
+      <c r="C828" s="3">
+        <v>15.77</v>
+      </c>
+      <c r="D828" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="829" ht="15" customHeight="1" spans="1:4">
@@ -12640,24 +12623,24 @@
         <v>62</v>
       </c>
       <c r="C829" s="3">
-        <v>16.3</v>
+        <v>15.79</v>
       </c>
       <c r="D829" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="830" ht="15" customHeight="1" spans="1:4">
-      <c r="A830" s="4">
+      <c r="A830" s="2">
         <v>978</v>
       </c>
-      <c r="B830" s="4">
+      <c r="B830" s="2">
         <v>62</v>
       </c>
-      <c r="C830" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D830" s="5">
-        <v>6.6</v>
+      <c r="C830" s="3">
+        <v>15.8</v>
+      </c>
+      <c r="D830" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="831" ht="15" customHeight="1" spans="1:4">
@@ -12668,24 +12651,24 @@
         <v>62</v>
       </c>
       <c r="C831" s="3">
-        <v>16.4</v>
+        <v>15.82</v>
       </c>
       <c r="D831" s="3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="832" ht="15" customHeight="1" spans="1:4">
-      <c r="A832" s="4">
+      <c r="A832" s="2">
         <v>980</v>
       </c>
-      <c r="B832" s="4">
+      <c r="B832" s="2">
         <v>62</v>
       </c>
-      <c r="C832" s="5">
-        <v>16.4</v>
-      </c>
-      <c r="D832" s="5">
-        <v>7.6</v>
+      <c r="C832" s="3">
+        <v>15.84</v>
+      </c>
+      <c r="D832" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="833" ht="15" customHeight="1" spans="1:4">
@@ -12696,24 +12679,24 @@
         <v>62</v>
       </c>
       <c r="C833" s="3">
-        <v>16.4</v>
+        <v>15.85</v>
       </c>
       <c r="D833" s="3">
-        <v>8.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="834" ht="15" customHeight="1" spans="1:4">
-      <c r="A834" s="4">
+      <c r="A834" s="2">
         <v>982</v>
       </c>
-      <c r="B834" s="4">
+      <c r="B834" s="2">
         <v>62</v>
       </c>
-      <c r="C834" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D834" s="5">
-        <v>6.7</v>
+      <c r="C834" s="3">
+        <v>15.87</v>
+      </c>
+      <c r="D834" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="835" ht="15" customHeight="1" spans="1:4">
@@ -12724,24 +12707,24 @@
         <v>62</v>
       </c>
       <c r="C835" s="3">
-        <v>16.5</v>
+        <v>15.89</v>
       </c>
       <c r="D835" s="3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="836" ht="15" customHeight="1" spans="1:4">
-      <c r="A836" s="4">
+      <c r="A836" s="2">
         <v>984</v>
       </c>
-      <c r="B836" s="4">
+      <c r="B836" s="2">
         <v>62</v>
       </c>
-      <c r="C836" s="5">
-        <v>16.5</v>
-      </c>
-      <c r="D836" s="5">
-        <v>7.7</v>
+      <c r="C836" s="3">
+        <v>15.9</v>
+      </c>
+      <c r="D836" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="837" ht="15" customHeight="1" spans="1:4">
@@ -12752,24 +12735,24 @@
         <v>62</v>
       </c>
       <c r="C837" s="3">
-        <v>16.5</v>
+        <v>15.92</v>
       </c>
       <c r="D837" s="3">
-        <v>8.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="838" ht="15" customHeight="1" spans="1:4">
-      <c r="A838" s="4">
+      <c r="A838" s="2">
         <v>986</v>
       </c>
-      <c r="B838" s="4">
+      <c r="B838" s="2">
         <v>62</v>
       </c>
-      <c r="C838" s="5">
-        <v>16.6</v>
-      </c>
-      <c r="D838" s="5">
-        <v>6.8</v>
+      <c r="C838" s="3">
+        <v>15.93</v>
+      </c>
+      <c r="D838" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="839" ht="15" customHeight="1" spans="1:4">
@@ -12780,24 +12763,24 @@
         <v>62</v>
       </c>
       <c r="C839" s="3">
-        <v>16.6</v>
+        <v>15.95</v>
       </c>
       <c r="D839" s="3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="840" ht="15" customHeight="1" spans="1:4">
-      <c r="A840" s="4">
+      <c r="A840" s="2">
         <v>988</v>
       </c>
-      <c r="B840" s="4">
+      <c r="B840" s="2">
         <v>62</v>
       </c>
-      <c r="C840" s="5">
-        <v>16.6</v>
-      </c>
-      <c r="D840" s="5">
-        <v>7.8</v>
+      <c r="C840" s="3">
+        <v>15.97</v>
+      </c>
+      <c r="D840" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="841" ht="15" customHeight="1" spans="1:4">
@@ -12808,24 +12791,24 @@
         <v>62</v>
       </c>
       <c r="C841" s="3">
-        <v>16.6</v>
+        <v>15.98</v>
       </c>
       <c r="D841" s="3">
-        <v>8.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="842" ht="15" customHeight="1" spans="1:4">
-      <c r="A842" s="4">
+      <c r="A842" s="2">
         <v>990</v>
       </c>
-      <c r="B842" s="4">
+      <c r="B842" s="2">
         <v>62</v>
       </c>
-      <c r="C842" s="5">
-        <v>16.7</v>
-      </c>
-      <c r="D842" s="5">
-        <v>6.9</v>
+      <c r="C842" s="3">
+        <v>16</v>
+      </c>
+      <c r="D842" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="843" ht="15" customHeight="1" spans="1:4">
@@ -12836,24 +12819,24 @@
         <v>62</v>
       </c>
       <c r="C843" s="3">
-        <v>16.7</v>
+        <v>16.02</v>
       </c>
       <c r="D843" s="3">
-        <v>7.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="844" ht="15" customHeight="1" spans="1:4">
-      <c r="A844" s="4">
+      <c r="A844" s="2">
         <v>992</v>
       </c>
-      <c r="B844" s="4">
+      <c r="B844" s="2">
         <v>62</v>
       </c>
-      <c r="C844" s="5">
-        <v>16.7</v>
-      </c>
-      <c r="D844" s="5">
-        <v>7.9</v>
+      <c r="C844" s="3">
+        <v>16.03</v>
+      </c>
+      <c r="D844" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="845" ht="15" customHeight="1" spans="1:4">
@@ -12864,23 +12847,23 @@
         <v>62</v>
       </c>
       <c r="C845" s="3">
-        <v>16.7</v>
+        <v>16.05</v>
       </c>
       <c r="D845" s="3">
-        <v>8.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="846" ht="15" customHeight="1" spans="1:4">
-      <c r="A846" s="4">
+      <c r="A846" s="2">
         <v>994</v>
       </c>
-      <c r="B846" s="4">
+      <c r="B846" s="2">
         <v>62</v>
       </c>
-      <c r="C846" s="5">
-        <v>16.8</v>
-      </c>
-      <c r="D846" s="5">
+      <c r="C846" s="3">
+        <v>16.07</v>
+      </c>
+      <c r="D846" s="3">
         <v>7</v>
       </c>
     </row>
@@ -12892,24 +12875,24 @@
         <v>62</v>
       </c>
       <c r="C847" s="3">
-        <v>16.8</v>
+        <v>16.08</v>
       </c>
       <c r="D847" s="3">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="848" ht="15" customHeight="1" spans="1:4">
-      <c r="A848" s="4">
+      <c r="A848" s="2">
         <v>996</v>
       </c>
-      <c r="B848" s="4">
+      <c r="B848" s="2">
         <v>62</v>
       </c>
-      <c r="C848" s="5">
-        <v>16.8</v>
-      </c>
-      <c r="D848" s="5">
-        <v>8</v>
+      <c r="C848" s="3">
+        <v>16.1</v>
+      </c>
+      <c r="D848" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="849" ht="15" customHeight="1" spans="1:4">
@@ -12920,24 +12903,24 @@
         <v>62</v>
       </c>
       <c r="C849" s="3">
-        <v>16.8</v>
+        <v>16.11</v>
       </c>
       <c r="D849" s="3">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="850" ht="15" customHeight="1" spans="1:4">
-      <c r="A850" s="4">
+      <c r="A850" s="2">
         <v>998</v>
       </c>
-      <c r="B850" s="4">
+      <c r="B850" s="2">
         <v>62</v>
       </c>
-      <c r="C850" s="5">
-        <v>16.9</v>
-      </c>
-      <c r="D850" s="5">
-        <v>7.1</v>
+      <c r="C850" s="3">
+        <v>16.13</v>
+      </c>
+      <c r="D850" s="3">
+        <v>7</v>
       </c>
     </row>
     <row r="851" ht="15" customHeight="1" spans="1:4">
@@ -12948,24 +12931,24 @@
         <v>62</v>
       </c>
       <c r="C851" s="3">
-        <v>16.9</v>
+        <v>16.15</v>
       </c>
       <c r="D851" s="3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="852" ht="15" customHeight="1" spans="1:4">
-      <c r="A852" s="4">
+      <c r="A852" s="2">
         <v>1000</v>
       </c>
-      <c r="B852" s="4">
+      <c r="B852" s="2">
         <v>62</v>
       </c>
-      <c r="C852" s="5">
-        <v>16.9</v>
-      </c>
-      <c r="D852" s="5">
-        <v>8.1</v>
+      <c r="C852" s="3">
+        <v>16.16</v>
+      </c>
+      <c r="D852" s="3">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
